--- a/database.xlsx
+++ b/database.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="159">
   <si>
     <t xml:space="preserve">alimento </t>
   </si>
@@ -44,9 +44,6 @@
     <t>grassi</t>
   </si>
   <si>
-    <t>saruri</t>
-  </si>
-  <si>
     <t>proteine</t>
   </si>
   <si>
@@ -402,16 +399,128 @@
   </si>
   <si>
     <t>acciughe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">croissant al cioccolato </t>
+  </si>
+  <si>
+    <t xml:space="preserve">panificio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bombolone krapfen </t>
+  </si>
+  <si>
+    <t>panificio</t>
+  </si>
+  <si>
+    <t>vecchio fornaio</t>
+  </si>
+  <si>
+    <t>pane arabo confezionato</t>
+  </si>
+  <si>
+    <t>saturi</t>
+  </si>
+  <si>
+    <t>pane per hamburger</t>
+  </si>
+  <si>
+    <t>piadina</t>
+  </si>
+  <si>
+    <t>roberto</t>
+  </si>
+  <si>
+    <t>uva</t>
+  </si>
+  <si>
+    <t>brimi</t>
+  </si>
+  <si>
+    <t>mozzarella armonia</t>
+  </si>
+  <si>
+    <t>rigoni</t>
+  </si>
+  <si>
+    <t>nocciolata</t>
+  </si>
+  <si>
+    <t>gelato 2 palline</t>
+  </si>
+  <si>
+    <t>gelataio</t>
+  </si>
+  <si>
+    <t>ferrero</t>
+  </si>
+  <si>
+    <t>nutella</t>
+  </si>
+  <si>
+    <t>macelleria</t>
+  </si>
+  <si>
+    <t>manzo bistecca cruda</t>
+  </si>
+  <si>
+    <t>mcDonalds</t>
+  </si>
+  <si>
+    <t>bigMac</t>
+  </si>
+  <si>
+    <t>patatine fritte</t>
+  </si>
+  <si>
+    <t>nugget</t>
+  </si>
+  <si>
+    <t>bigTasty bacon</t>
+  </si>
+  <si>
+    <t>gran crispy bacon</t>
+  </si>
+  <si>
+    <t>pomodorini</t>
+  </si>
+  <si>
+    <t>mareblu</t>
+  </si>
+  <si>
+    <t>tonno olio oliva sgocciolato</t>
+  </si>
+  <si>
+    <t>jocca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fiocchi latte </t>
+  </si>
+  <si>
+    <t>gorgonzola</t>
+  </si>
+  <si>
+    <t>muller</t>
+  </si>
+  <si>
+    <t>soffio yogurt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -437,11 +546,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -776,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K90"/>
+  <dimension ref="A2:K112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -788,16 +898,16 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>1</v>
@@ -812,21 +922,21 @@
         <v>4</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="15">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>150</v>
@@ -856,12 +966,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" ht="15">
       <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
         <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
@@ -888,9 +998,9 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="15">
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -917,12 +1027,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" ht="15">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
       </c>
       <c r="C7" s="1">
         <v>90</v>
@@ -952,12 +1062,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" ht="15">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -986,10 +1096,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1">
         <v>56</v>
@@ -1019,12 +1129,12 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" ht="15">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>90</v>
@@ -1054,12 +1164,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" ht="15">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1">
         <v>23</v>
@@ -1089,12 +1199,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" ht="15">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
@@ -1121,12 +1231,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" ht="15">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
@@ -1153,12 +1263,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" ht="15">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" s="1">
         <v>140</v>
@@ -1188,12 +1298,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>140</v>
@@ -1223,12 +1333,12 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" ht="15">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1">
         <v>140</v>
@@ -1258,12 +1368,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" ht="15">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="1">
         <v>140</v>
@@ -1293,12 +1403,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" ht="15">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1">
         <v>140</v>
@@ -1328,12 +1438,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" ht="15">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1">
         <v>140</v>
@@ -1354,9 +1464,9 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" ht="15">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
@@ -1380,12 +1490,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="15">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1">
         <v>100</v>
@@ -1415,9 +1525,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" ht="15">
       <c r="B22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="1">
         <v>100</v>
@@ -1447,12 +1557,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" ht="15">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1">
         <v>100</v>
@@ -1482,12 +1592,12 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" ht="15">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="1">
         <v>100</v>
@@ -1517,12 +1627,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" ht="15">
       <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
         <v>75</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
       </c>
       <c r="C25" s="1">
         <v>300</v>
@@ -1552,12 +1662,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" ht="15">
       <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s">
         <v>77</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
       </c>
       <c r="C26" s="1">
         <v>330</v>
@@ -1587,12 +1697,12 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" ht="15">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="1">
         <v>125</v>
@@ -1622,12 +1732,12 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" ht="15">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
@@ -1654,12 +1764,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" ht="15">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
@@ -1686,9 +1796,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" ht="15">
       <c r="B30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
@@ -1715,12 +1825,12 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" ht="15">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
@@ -1747,12 +1857,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" ht="15">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
@@ -1779,12 +1889,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" ht="15">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
@@ -1811,12 +1921,12 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" ht="15">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
@@ -1843,12 +1953,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" ht="15">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
@@ -1875,82 +1985,48 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="36" spans="1:11" ht="15"/>
+    <row r="37" spans="1:11" ht="15">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="1">
+        <v>75</v>
+      </c>
+      <c r="D37" s="1">
+        <v>100</v>
+      </c>
+      <c r="E37" s="1">
+        <v>130</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2</v>
+      </c>
+      <c r="J37" s="1">
+        <v>21</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15">
+      <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
         <v>29</v>
-      </c>
-      <c r="C36" s="1">
-        <v>75</v>
-      </c>
-      <c r="D36" s="1">
-        <v>100</v>
-      </c>
-      <c r="E36" s="1">
-        <v>130</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I36" s="1">
-        <v>2</v>
-      </c>
-      <c r="J36" s="1">
-        <v>21</v>
-      </c>
-      <c r="K36" s="1">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="1">
-        <v>140</v>
-      </c>
-      <c r="D37" s="1">
-        <v>100</v>
-      </c>
-      <c r="E37" s="1">
-        <v>118</v>
-      </c>
-      <c r="F37" s="1">
-        <v>21.1</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="J37" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" t="s">
-        <v>31</v>
       </c>
       <c r="C38" s="1">
         <v>140</v>
@@ -1959,1480 +2035,2277 @@
         <v>100</v>
       </c>
       <c r="E38" s="1">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F38" s="1">
-        <v>17.899999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="G38" s="1">
-        <v>4.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="I38" s="1">
         <v>0.2</v>
       </c>
       <c r="J38" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15">
+      <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="1">
+        <v>140</v>
+      </c>
+      <c r="D39" s="1">
+        <v>100</v>
+      </c>
+      <c r="E39" s="1">
+        <v>115</v>
+      </c>
+      <c r="F39" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J39" s="1">
         <v>4.8</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K39" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
-      <c r="A39" t="s">
+    <row r="40" spans="1:11" ht="15">
+      <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="1">
+        <v>100</v>
+      </c>
+      <c r="E40" s="1">
+        <v>376</v>
+      </c>
+      <c r="F40" s="1">
+        <v>69.3</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J40" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15">
+      <c r="A41" t="s">
         <v>86</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="1">
+        <v>100</v>
+      </c>
+      <c r="E41" s="1">
+        <v>47</v>
+      </c>
+      <c r="F41" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G41" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J41" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="1">
-        <v>100</v>
-      </c>
-      <c r="E39" s="1">
-        <v>376</v>
-      </c>
-      <c r="F39" s="1">
-        <v>69.3</v>
-      </c>
-      <c r="G39" s="1">
+      <c r="D42" s="1">
+        <v>100</v>
+      </c>
+      <c r="E42" s="1">
+        <v>151</v>
+      </c>
+      <c r="F42" s="1">
+        <v>31</v>
+      </c>
+      <c r="H42" s="1">
         <v>0.8</v>
       </c>
-      <c r="H39" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="J39" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="1">
-        <v>100</v>
-      </c>
-      <c r="E40" s="1">
-        <v>47</v>
-      </c>
-      <c r="F40" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G40" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H40" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="I40" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J40" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="J42" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="1">
-        <v>100</v>
-      </c>
-      <c r="E41" s="1">
-        <v>151</v>
-      </c>
-      <c r="F41" s="1">
-        <v>31</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="J41" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="B42" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="1">
-        <v>100</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D43" s="1">
+        <v>100</v>
+      </c>
+      <c r="E43" s="1">
         <v>253</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F43" s="1">
         <v>55.4</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G43" s="1">
         <v>1.5</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H43" s="1">
         <v>1</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="J42" s="1">
-        <v>9</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="1">
-        <v>100</v>
-      </c>
-      <c r="E43" s="1">
-        <v>30</v>
-      </c>
-      <c r="F43" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G43" s="1">
-        <v>3.9</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0.1</v>
       </c>
       <c r="I43" s="1">
         <v>0.1</v>
       </c>
       <c r="J43" s="1">
+        <v>9</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15">
+      <c r="A44" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="1">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1">
+        <v>30</v>
+      </c>
+      <c r="F44" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G44" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J44" s="1">
         <v>1.2</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K44" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
-      <c r="B44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44" s="1">
-        <v>100</v>
-      </c>
-      <c r="E44" s="1">
+    <row r="45" spans="1:11" ht="15">
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="1">
+        <v>100</v>
+      </c>
+      <c r="E45" s="1">
         <v>129</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
         <v>13</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I45" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J45" s="1">
         <v>0.5</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K45" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
-      <c r="B45" t="s">
-        <v>36</v>
-      </c>
-      <c r="D45" s="1">
-        <v>100</v>
-      </c>
-      <c r="E45" s="1">
-        <v>72</v>
-      </c>
-      <c r="F45" s="1">
-        <v>16</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>2</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" ht="15">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>156</v>
+      </c>
+      <c r="C46" s="1">
+        <v>30</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="F46" s="1">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="I46" s="1">
-        <v>0.6</v>
+        <v>19</v>
       </c>
       <c r="J46" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>158</v>
+      </c>
+      <c r="C47" s="1">
+        <v>150</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1">
-        <v>350</v>
+        <v>108</v>
       </c>
       <c r="F47" s="1">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="G47" s="1">
-        <v>3.8</v>
+        <v>14</v>
       </c>
       <c r="H47" s="1">
-        <v>34</v>
+        <v>3.6</v>
       </c>
       <c r="I47" s="1">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J47" s="1">
         <v>3.7</v>
       </c>
       <c r="K47" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15">
+      <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="1">
+        <v>100</v>
+      </c>
+      <c r="E48" s="1">
+        <v>72</v>
+      </c>
+      <c r="F48" s="1">
+        <v>16</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="15">
+      <c r="A49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="1">
+        <v>100</v>
+      </c>
+      <c r="E49" s="1">
+        <v>162</v>
+      </c>
+      <c r="F49" s="1">
+        <v>24</v>
+      </c>
+      <c r="H49" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J49" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15">
+      <c r="A50" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="1">
+        <v>100</v>
+      </c>
+      <c r="E50" s="1">
+        <v>350</v>
+      </c>
+      <c r="F50" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="H50" s="1">
+        <v>34</v>
+      </c>
+      <c r="I50" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J50" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="K50" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
-      <c r="B48" t="s">
+    <row r="51" spans="1:11" ht="15">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="1">
+        <v>100</v>
+      </c>
+      <c r="E51" s="1">
+        <v>96</v>
+      </c>
+      <c r="F51" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="H51" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I51" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="J51" s="1">
+        <v>10</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="15">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="1">
+        <v>100</v>
+      </c>
+      <c r="E52" s="1">
+        <v>100</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>6</v>
+      </c>
+      <c r="I52" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J52" s="1">
+        <v>10</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15">
+      <c r="B53" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="1">
+        <v>280</v>
+      </c>
+      <c r="D53" s="1">
+        <v>100</v>
+      </c>
+      <c r="E53" s="1">
+        <v>127</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J53" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15">
+      <c r="B54" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="1">
-        <v>280</v>
-      </c>
-      <c r="D48" s="1">
-        <v>100</v>
-      </c>
-      <c r="E48" s="1">
-        <v>127</v>
-      </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I48" s="1">
+      <c r="C54" s="1">
+        <v>190</v>
+      </c>
+      <c r="D54" s="1">
+        <v>100</v>
+      </c>
+      <c r="E54" s="1">
+        <v>144</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J54" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15">
+      <c r="A55" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="1">
+        <v>100</v>
+      </c>
+      <c r="E55" s="1">
+        <v>123</v>
+      </c>
+      <c r="F55" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H55" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="I55" s="1">
         <v>0.8</v>
       </c>
-      <c r="J48" s="1">
-        <v>20.5</v>
-      </c>
-      <c r="K48" s="1">
+      <c r="J55" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15">
+      <c r="B56" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="1">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1">
+        <v>86</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G56" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="B49" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" s="1">
-        <v>190</v>
-      </c>
-      <c r="D49" s="1">
-        <v>100</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="H56" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J56" s="1">
+        <v>20</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15">
+      <c r="A57" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="1">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1">
+        <v>241</v>
+      </c>
+      <c r="F57" s="1">
+        <v>59</v>
+      </c>
+      <c r="G57" s="1">
+        <v>56</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="15">
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="1">
+        <v>100</v>
+      </c>
+      <c r="E58" s="1">
+        <v>65</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J58" s="1">
+        <v>14.2</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" s="1">
+        <v>60</v>
+      </c>
+      <c r="D59" s="1">
+        <v>100</v>
+      </c>
+      <c r="E59" s="1">
+        <v>245</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>17</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J59" s="1">
+        <v>23</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15">
+      <c r="A60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" s="1">
+        <v>100</v>
+      </c>
+      <c r="D60" s="1">
+        <v>100</v>
+      </c>
+      <c r="E60" s="1">
+        <v>224</v>
+      </c>
+      <c r="F60" s="1">
+        <v>17</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H60" s="1">
+        <v>12</v>
+      </c>
+      <c r="I60" s="1">
+        <v>12</v>
+      </c>
+      <c r="J60" s="1">
+        <v>12</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15">
+      <c r="A61" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="1">
+        <v>125</v>
+      </c>
+      <c r="D61" s="1">
+        <v>100</v>
+      </c>
+      <c r="E61" s="1">
+        <v>225</v>
+      </c>
+      <c r="F61" s="1">
+        <v>12</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H61" s="1">
+        <v>13</v>
+      </c>
+      <c r="I61" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J61" s="1">
+        <v>15</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="15" customHeight="1">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="1">
+        <v>100</v>
+      </c>
+      <c r="E62" s="1">
+        <v>104</v>
+      </c>
+      <c r="F62" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G62" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J62" s="1">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="K62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15">
+      <c r="B63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="1">
+        <v>70</v>
+      </c>
+      <c r="D63" s="1">
+        <v>100</v>
+      </c>
+      <c r="E63" s="1">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="G63" s="1">
+        <v>9</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="15">
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" ht="15">
+      <c r="B65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" s="1">
+        <v>150</v>
+      </c>
+      <c r="D65" s="1">
+        <v>100</v>
+      </c>
+      <c r="E65" s="1">
+        <v>93</v>
+      </c>
+      <c r="F65" s="1">
+        <v>20</v>
+      </c>
+      <c r="G65" s="1">
+        <v>17.3</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" ht="15">
+      <c r="B66" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1">
+        <v>180</v>
+      </c>
+      <c r="D66" s="1">
+        <v>100</v>
+      </c>
+      <c r="E66" s="1">
+        <v>52</v>
+      </c>
+      <c r="F66" s="1">
+        <v>14</v>
+      </c>
+      <c r="G66" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" ht="15">
+      <c r="B67" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="1">
+        <v>100</v>
+      </c>
+      <c r="E67" s="1">
+        <v>34</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G67" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" ht="15">
+      <c r="B68" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" s="1">
+        <v>100</v>
+      </c>
+      <c r="D68" s="1">
+        <v>100</v>
+      </c>
+      <c r="E68" s="1">
+        <v>37</v>
+      </c>
+      <c r="F68" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" ht="15">
+      <c r="B69" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="1">
+        <v>12</v>
+      </c>
+      <c r="D69" s="1">
+        <v>100</v>
+      </c>
+      <c r="E69" s="1">
+        <v>32</v>
+      </c>
+      <c r="F69" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" ht="15">
+      <c r="B70" t="s">
+        <v>115</v>
+      </c>
+      <c r="C70" s="1">
+        <v>150</v>
+      </c>
+      <c r="D70" s="1">
+        <v>100</v>
+      </c>
+      <c r="E70" s="1">
+        <v>25</v>
+      </c>
+      <c r="F70" s="1">
+        <v>5</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" ht="15">
+      <c r="B71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71" s="1">
+        <v>150</v>
+      </c>
+      <c r="D71" s="1">
+        <v>100</v>
+      </c>
+      <c r="E71" s="1">
+        <v>69</v>
+      </c>
+      <c r="F71" s="1">
+        <v>18</v>
+      </c>
+      <c r="G71" s="1">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" ht="15">
+      <c r="B72" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" ht="15">
+      <c r="B73" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73" s="1">
+        <v>21</v>
+      </c>
+      <c r="D73" s="1">
+        <v>100</v>
+      </c>
+      <c r="E73" s="1">
+        <v>36</v>
+      </c>
+      <c r="F73" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" ht="15">
+      <c r="B74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" ht="15">
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" s="1">
+        <v>100</v>
+      </c>
+      <c r="E75" s="1">
+        <v>34</v>
+      </c>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <v>3</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" ht="15">
+      <c r="B76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76" s="1">
+        <v>130</v>
+      </c>
+      <c r="D76" s="1">
+        <v>100</v>
+      </c>
+      <c r="E76" s="1">
+        <v>41</v>
+      </c>
+      <c r="F76" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" ht="15">
+      <c r="B77" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" s="1">
+        <v>250</v>
+      </c>
+      <c r="D77" s="1">
+        <v>100</v>
+      </c>
+      <c r="E77" s="1">
+        <v>15</v>
+      </c>
+      <c r="F77" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" ht="15">
+      <c r="B78" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" s="1">
+        <v>260</v>
+      </c>
+      <c r="D78" s="1">
+        <v>100</v>
+      </c>
+      <c r="E78" s="1">
+        <v>17</v>
+      </c>
+      <c r="F78" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" ht="15">
+      <c r="B79" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" ht="15">
+      <c r="B80" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="15">
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="15">
+      <c r="A82" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" t="s">
+        <v>95</v>
+      </c>
+      <c r="C82" s="1">
+        <v>125</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1">
+        <v>140</v>
+      </c>
+      <c r="F82" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="H82" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="J82" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="15">
+      <c r="A83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" s="1">
+        <v>125</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
+      </c>
+      <c r="E83" s="1">
+        <v>275</v>
+      </c>
+      <c r="F83" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="H83" s="1">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="J83" s="1">
+        <v>21</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="15">
+      <c r="B84" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" s="1">
+        <v>140</v>
+      </c>
+      <c r="D84" s="1">
+        <v>100</v>
+      </c>
+      <c r="E84" s="1">
+        <v>146</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="I84" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J84" s="1">
+        <v>21</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="15">
+      <c r="A85" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="1">
+        <v>100</v>
+      </c>
+      <c r="E85" s="1">
+        <v>553</v>
+      </c>
+      <c r="F85" s="1">
+        <v>28</v>
+      </c>
+      <c r="G85" s="1">
+        <v>20</v>
+      </c>
+      <c r="H85" s="1">
+        <v>42</v>
+      </c>
+      <c r="I85" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="J85" s="1">
+        <v>13</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="15">
+      <c r="A86" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="1">
+        <v>100</v>
+      </c>
+      <c r="E86" s="1">
+        <v>364</v>
+      </c>
+      <c r="F86" s="1">
+        <v>60</v>
+      </c>
+      <c r="G86" s="1">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J86" s="1">
+        <v>12</v>
+      </c>
+      <c r="K86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="15">
+      <c r="A87" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" t="s">
+        <v>101</v>
+      </c>
+      <c r="D87" s="1">
+        <v>100</v>
+      </c>
+      <c r="E87" s="1">
+        <v>608</v>
+      </c>
+      <c r="F87" s="1">
+        <v>12</v>
+      </c>
+      <c r="G87" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="H87" s="1">
+        <v>47</v>
+      </c>
+      <c r="I87" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="J87" s="1">
+        <v>30</v>
+      </c>
+      <c r="K87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="15">
+      <c r="B88" t="s">
+        <v>102</v>
+      </c>
+      <c r="C88" s="1">
+        <v>125</v>
+      </c>
+      <c r="D88" s="1">
+        <v>100</v>
+      </c>
+      <c r="E88" s="1">
+        <v>192</v>
+      </c>
+      <c r="F88" s="1">
+        <v>11</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="H88" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J88" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="K88" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="15">
+      <c r="A89" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89" s="1">
+        <v>100</v>
+      </c>
+      <c r="E89" s="1">
+        <v>421</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1">
+        <v>39</v>
+      </c>
+      <c r="I89" s="1">
+        <v>27</v>
+      </c>
+      <c r="J89" s="1">
+        <v>23</v>
+      </c>
+      <c r="K89" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="15">
+      <c r="A90" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90" t="s">
+        <v>108</v>
+      </c>
+      <c r="D90" s="1">
+        <v>100</v>
+      </c>
+      <c r="E90" s="1">
+        <v>54</v>
+      </c>
+      <c r="F90" s="1">
+        <v>12</v>
+      </c>
+      <c r="G90" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15">
+      <c r="A91" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" t="s">
+        <v>109</v>
+      </c>
+      <c r="D91" s="1">
+        <v>100</v>
+      </c>
+      <c r="E91" s="1">
+        <v>683</v>
+      </c>
+      <c r="F91" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="H91" s="1">
+        <v>66</v>
+      </c>
+      <c r="I91" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J91" s="1">
+        <v>14</v>
+      </c>
+      <c r="K91" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="15">
+      <c r="A92" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" t="s">
+        <v>110</v>
+      </c>
+      <c r="C92" s="1">
+        <v>150</v>
+      </c>
+      <c r="D92" s="1">
+        <v>100</v>
+      </c>
+      <c r="E92" s="1">
+        <v>54</v>
+      </c>
+      <c r="F92" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G92" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I92" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J92" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="K92" s="1">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="15">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="1">
+        <v>100</v>
+      </c>
+      <c r="D93" s="1">
+        <v>100</v>
+      </c>
+      <c r="E93" s="1">
+        <v>98</v>
+      </c>
+      <c r="F93" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H93" s="1">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J93" s="1">
+        <v>19</v>
+      </c>
+      <c r="K93" s="1">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="15">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" s="1">
+        <v>100</v>
+      </c>
+      <c r="D94" s="1">
+        <v>100</v>
+      </c>
+      <c r="E94" s="1">
+        <v>91</v>
+      </c>
+      <c r="F94" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I94" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J94" s="1">
+        <v>17</v>
+      </c>
+      <c r="K94" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="15">
+      <c r="A95" t="s">
+        <v>120</v>
+      </c>
+      <c r="B95" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" s="1">
+        <v>300</v>
+      </c>
+      <c r="D95" s="1">
+        <v>100</v>
+      </c>
+      <c r="E95" s="1">
+        <v>134</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H95" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I95" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J95" s="1">
+        <v>21</v>
+      </c>
+      <c r="K95" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="15">
+      <c r="A96" t="s">
+        <v>58</v>
+      </c>
+      <c r="B96" t="s">
+        <v>122</v>
+      </c>
+      <c r="D96" s="1">
+        <v>100</v>
+      </c>
+      <c r="E96" s="1">
+        <v>67</v>
+      </c>
+      <c r="F96" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G96" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="H96" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="I96" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J96" s="1">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="15">
+      <c r="A97" t="s">
+        <v>65</v>
+      </c>
+      <c r="B97" t="s">
+        <v>123</v>
+      </c>
+      <c r="C97" s="1">
+        <v>20</v>
+      </c>
+      <c r="D97" s="1">
+        <v>100</v>
+      </c>
+      <c r="E97" s="1">
+        <v>451</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
+        <v>44</v>
+      </c>
+      <c r="I97" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="J97" s="1">
+        <v>13</v>
+      </c>
+      <c r="K97" s="1">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="15">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" s="1">
+        <v>70</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1</v>
+      </c>
+      <c r="E98" s="1">
+        <v>295</v>
+      </c>
+      <c r="F98" s="1">
+        <v>34</v>
+      </c>
+      <c r="G98" s="1">
+        <v>13</v>
+      </c>
+      <c r="H98" s="1">
+        <v>16</v>
+      </c>
+      <c r="I98" s="1">
+        <v>8</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K98" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="15">
+      <c r="A99" t="s">
+        <v>125</v>
+      </c>
+      <c r="B99" t="s">
+        <v>126</v>
+      </c>
+      <c r="C99" s="1">
+        <v>75</v>
+      </c>
+      <c r="D99" s="1">
+        <v>1</v>
+      </c>
+      <c r="E99" s="1">
+        <v>330</v>
+      </c>
+      <c r="F99" s="1">
+        <v>38</v>
+      </c>
+      <c r="G99" s="1">
+        <v>15</v>
+      </c>
+      <c r="H99" s="1">
+        <v>17</v>
+      </c>
+      <c r="I99" s="1">
+        <v>8</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K99" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>128</v>
+      </c>
+      <c r="B100" t="s">
+        <v>129</v>
+      </c>
+      <c r="C100" s="1">
+        <v>75</v>
+      </c>
+      <c r="D100" s="1">
+        <v>100</v>
+      </c>
+      <c r="E100" s="1">
+        <v>259</v>
+      </c>
+      <c r="F100" s="1">
+        <v>54</v>
+      </c>
+      <c r="G100" s="1">
+        <v>23</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="K100" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" s="1">
+        <v>75</v>
+      </c>
+      <c r="D101" s="1">
+        <v>100</v>
+      </c>
+      <c r="E101" s="1">
+        <v>278</v>
+      </c>
+      <c r="F101" s="1">
+        <v>44</v>
+      </c>
+      <c r="G101" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H101" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="J101" s="1">
+        <v>11</v>
+      </c>
+      <c r="K101" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>133</v>
+      </c>
+      <c r="B102" t="s">
+        <v>132</v>
+      </c>
+      <c r="C102" s="1">
+        <v>110</v>
+      </c>
+      <c r="D102" s="1">
+        <v>100</v>
+      </c>
+      <c r="E102" s="1">
+        <v>313</v>
+      </c>
+      <c r="F102" s="1">
+        <v>49</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H102" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="J102" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="K102" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>135</v>
+      </c>
+      <c r="B103" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" s="1">
+        <v>100</v>
+      </c>
+      <c r="D103" s="1">
+        <v>100</v>
+      </c>
+      <c r="E103" s="1">
+        <v>167</v>
+      </c>
+      <c r="F103" s="1">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H103" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="I103" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="J103" s="1">
+        <v>17</v>
+      </c>
+      <c r="K103" s="1">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>137</v>
+      </c>
+      <c r="B104" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" s="1">
+        <v>15</v>
+      </c>
+      <c r="D104" s="1">
+        <v>100</v>
+      </c>
+      <c r="E104" s="1">
+        <v>544</v>
+      </c>
+      <c r="F104" s="1">
+        <v>54</v>
+      </c>
+      <c r="G104" s="1">
+        <v>51</v>
+      </c>
+      <c r="H104" s="1">
+        <v>32</v>
+      </c>
+      <c r="I104" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="J104" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="K104" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" s="1">
+        <v>70</v>
+      </c>
+      <c r="D105" s="1">
+        <v>100</v>
+      </c>
+      <c r="E105" s="1">
+        <v>225</v>
+      </c>
+      <c r="F105" s="1">
+        <v>28</v>
+      </c>
+      <c r="G105" s="1">
+        <v>26</v>
+      </c>
+      <c r="H105" s="1">
+        <v>11</v>
+      </c>
+      <c r="I105" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="J105" s="1">
+        <v>3</v>
+      </c>
+      <c r="K105" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" t="s">
+        <v>141</v>
+      </c>
+      <c r="B106" t="s">
+        <v>142</v>
+      </c>
+      <c r="C106" s="1">
+        <v>15</v>
+      </c>
+      <c r="D106" s="1">
+        <v>100</v>
+      </c>
+      <c r="E106" s="1">
+        <v>540</v>
+      </c>
+      <c r="F106" s="1">
+        <v>58</v>
+      </c>
+      <c r="G106" s="1">
+        <v>56</v>
+      </c>
+      <c r="H106" s="1">
+        <v>30.9</v>
+      </c>
+      <c r="I106" s="1">
+        <v>11</v>
+      </c>
+      <c r="J106" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="K106" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" t="s">
+        <v>143</v>
+      </c>
+      <c r="B107" t="s">
         <v>144</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="I49" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J49" s="1">
-        <v>19.7</v>
-      </c>
-      <c r="K49" s="1">
+      <c r="C107" s="1">
+        <v>130</v>
+      </c>
+      <c r="D107" s="1">
+        <v>100</v>
+      </c>
+      <c r="E107" s="1">
+        <v>150</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="I107" s="1">
+        <v>3</v>
+      </c>
+      <c r="J107" s="1">
+        <v>23</v>
+      </c>
+      <c r="K107" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
-      <c r="A50" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="1">
-        <v>100</v>
-      </c>
-      <c r="E50" s="1">
-        <v>123</v>
-      </c>
-      <c r="F50" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="G50" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="H50" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="I50" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="J50" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="B51" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" s="1">
-        <v>100</v>
-      </c>
-      <c r="E51" s="1">
-        <v>86</v>
-      </c>
-      <c r="F51" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="G51" s="1">
+    <row r="108" spans="1:11">
+      <c r="A108" t="s">
+        <v>145</v>
+      </c>
+      <c r="B108" t="s">
+        <v>146</v>
+      </c>
+      <c r="C108" s="1">
+        <v>230</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1</v>
+      </c>
+      <c r="E108" s="1">
+        <v>513</v>
+      </c>
+      <c r="F108" s="1">
+        <v>42</v>
+      </c>
+      <c r="G108" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="H108" s="1">
+        <v>27</v>
+      </c>
+      <c r="I108" s="1">
+        <v>10</v>
+      </c>
+      <c r="J108" s="1">
+        <v>27</v>
+      </c>
+      <c r="K108" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" t="s">
+        <v>145</v>
+      </c>
+      <c r="B109" t="s">
+        <v>147</v>
+      </c>
+      <c r="C109" s="1">
+        <v>70</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1</v>
+      </c>
+      <c r="E109" s="1">
+        <v>229</v>
+      </c>
+      <c r="F109" s="1">
+        <v>30</v>
+      </c>
+      <c r="G109" s="1">
         <v>0.1</v>
       </c>
-      <c r="H51" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I51" s="1">
+      <c r="H109" s="1">
+        <v>11</v>
+      </c>
+      <c r="I109" s="1">
+        <v>2</v>
+      </c>
+      <c r="J109" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K109" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" t="s">
+        <v>148</v>
+      </c>
+      <c r="C110" s="1">
+        <v>16</v>
+      </c>
+      <c r="D110" s="1">
+        <v>100</v>
+      </c>
+      <c r="E110" s="1">
+        <v>302</v>
+      </c>
+      <c r="F110" s="1">
+        <v>15</v>
+      </c>
+      <c r="G110" s="1">
         <v>0.1</v>
       </c>
-      <c r="J51" s="1">
+      <c r="H110" s="1">
         <v>20</v>
       </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="1">
-        <v>100</v>
-      </c>
-      <c r="E52" s="1">
-        <v>241</v>
-      </c>
-      <c r="F52" s="1">
-        <v>59</v>
-      </c>
-      <c r="G52" s="1">
-        <v>56</v>
-      </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="B53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D53" s="1">
-        <v>100</v>
-      </c>
-      <c r="E53" s="1">
-        <v>65</v>
-      </c>
-      <c r="F53" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0</v>
-      </c>
-      <c r="H53" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I53" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="J53" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="I110" s="1">
+        <v>5</v>
+      </c>
+      <c r="J110" s="1">
+        <v>16</v>
+      </c>
+      <c r="K110" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" t="s">
+        <v>145</v>
+      </c>
+      <c r="B111" t="s">
+        <v>149</v>
+      </c>
+      <c r="C111" s="1">
+        <v>360</v>
+      </c>
+      <c r="D111" s="1">
+        <v>1</v>
+      </c>
+      <c r="E111" s="1">
+        <v>914</v>
+      </c>
+      <c r="F111" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="G111" s="1">
+        <v>12</v>
+      </c>
+      <c r="H111" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="I111" s="1">
+        <v>22</v>
+      </c>
+      <c r="J111" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="K111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
+        <v>145</v>
+      </c>
+      <c r="B112" t="s">
+        <v>150</v>
+      </c>
+      <c r="C112" s="1">
+        <v>240</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1</v>
+      </c>
+      <c r="E112" s="1">
+        <v>754</v>
+      </c>
+      <c r="F112" s="1">
         <v>41</v>
       </c>
-      <c r="C55" s="1">
-        <v>100</v>
-      </c>
-      <c r="D55" s="1">
-        <v>100</v>
-      </c>
-      <c r="E55" s="1">
-        <v>224</v>
-      </c>
-      <c r="F55" s="1">
-        <v>17</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H55" s="1">
-        <v>12</v>
-      </c>
-      <c r="I55" s="1">
-        <v>12</v>
-      </c>
-      <c r="J55" s="1">
-        <v>12</v>
-      </c>
-      <c r="K55" s="1">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" t="s">
-        <v>72</v>
-      </c>
-      <c r="B56" t="s">
-        <v>42</v>
-      </c>
-      <c r="C56" s="1">
-        <v>125</v>
-      </c>
-      <c r="D56" s="1">
-        <v>100</v>
-      </c>
-      <c r="E56" s="1">
-        <v>225</v>
-      </c>
-      <c r="F56" s="1">
-        <v>12</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H56" s="1">
-        <v>13</v>
-      </c>
-      <c r="I56" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J56" s="1">
-        <v>15</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="15" customHeight="1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-      <c r="B57" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="1">
-        <v>100</v>
-      </c>
-      <c r="E57" s="1">
-        <v>104</v>
-      </c>
-      <c r="F57" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="G57" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="H57" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="J57" s="1">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="K57" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="B58" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" s="1">
-        <v>70</v>
-      </c>
-      <c r="D58" s="1">
-        <v>100</v>
-      </c>
-      <c r="E58" s="1">
-        <v>61</v>
-      </c>
-      <c r="F58" s="1">
-        <v>14.7</v>
-      </c>
-      <c r="G58" s="1">
-        <v>9</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="B59" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="B60" t="s">
-        <v>45</v>
-      </c>
-      <c r="C60" s="1">
-        <v>150</v>
-      </c>
-      <c r="D60" s="1">
-        <v>100</v>
-      </c>
-      <c r="E60" s="1">
-        <v>93</v>
-      </c>
-      <c r="F60" s="1">
-        <v>20</v>
-      </c>
-      <c r="G60" s="1">
-        <v>17.3</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="B61" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="1">
-        <v>180</v>
-      </c>
-      <c r="D61" s="1">
-        <v>100</v>
-      </c>
-      <c r="E61" s="1">
-        <v>52</v>
-      </c>
-      <c r="F61" s="1">
-        <v>14</v>
-      </c>
-      <c r="G61" s="1">
-        <v>10.4</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="B62" t="s">
-        <v>47</v>
-      </c>
-      <c r="D62" s="1">
-        <v>100</v>
-      </c>
-      <c r="E62" s="1">
-        <v>34</v>
-      </c>
-      <c r="F62" s="1">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="G62" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="B63" t="s">
+      <c r="G112" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="H112" s="1">
         <v>48</v>
       </c>
-      <c r="C63" s="1">
-        <v>12</v>
-      </c>
-      <c r="D63" s="1">
-        <v>100</v>
-      </c>
-      <c r="E63" s="1">
-        <v>32</v>
-      </c>
-      <c r="F63" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="G63" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="H63" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I63" s="1">
-        <v>0</v>
-      </c>
-      <c r="J63" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="B64" t="s">
-        <v>116</v>
-      </c>
-      <c r="C64" s="1">
-        <v>150</v>
-      </c>
-      <c r="D64" s="1">
-        <v>100</v>
-      </c>
-      <c r="E64" s="1">
-        <v>25</v>
-      </c>
-      <c r="F64" s="1">
-        <v>5</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2</v>
-      </c>
-      <c r="H64" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1">
-        <v>1.9</v>
-      </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="B65" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="B66" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="1">
-        <v>21</v>
-      </c>
-      <c r="D66" s="1">
-        <v>100</v>
-      </c>
-      <c r="E66" s="1">
-        <v>36</v>
-      </c>
-      <c r="F66" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
-      <c r="B67" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="B68" t="s">
-        <v>52</v>
-      </c>
-      <c r="D68" s="1">
-        <v>100</v>
-      </c>
-      <c r="E68" s="1">
-        <v>34</v>
-      </c>
-      <c r="F68" s="1">
-        <v>3</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1">
-        <v>3</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="B69" t="s">
-        <v>53</v>
-      </c>
-      <c r="C69" s="1">
-        <v>130</v>
-      </c>
-      <c r="D69" s="1">
-        <v>100</v>
-      </c>
-      <c r="E69" s="1">
+      <c r="I112" s="1">
+        <v>18</v>
+      </c>
+      <c r="J112" s="1">
         <v>41</v>
       </c>
-      <c r="F69" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="G69" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I69" s="1">
-        <v>0</v>
-      </c>
-      <c r="J69" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="B70" t="s">
-        <v>54</v>
-      </c>
-      <c r="C70" s="1">
-        <v>250</v>
-      </c>
-      <c r="D70" s="1">
-        <v>100</v>
-      </c>
-      <c r="E70" s="1">
-        <v>15</v>
-      </c>
-      <c r="F70" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="G70" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="H70" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0</v>
-      </c>
-      <c r="J70" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="B71" t="s">
-        <v>117</v>
-      </c>
-      <c r="C71" s="1">
-        <v>260</v>
-      </c>
-      <c r="D71" s="1">
-        <v>100</v>
-      </c>
-      <c r="E71" s="1">
-        <v>17</v>
-      </c>
-      <c r="F71" s="1">
-        <v>3.1</v>
-      </c>
-      <c r="G71" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I71" s="1">
-        <v>0</v>
-      </c>
-      <c r="J71" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="B72" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="B73" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
-      <c r="B74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
-      <c r="A75" t="s">
-        <v>87</v>
-      </c>
-      <c r="B75" t="s">
-        <v>96</v>
-      </c>
-      <c r="C75" s="1">
-        <v>125</v>
-      </c>
-      <c r="D75" s="1">
-        <v>1</v>
-      </c>
-      <c r="E75" s="1">
-        <v>140</v>
-      </c>
-      <c r="F75" s="1">
-        <v>18.8</v>
-      </c>
-      <c r="H75" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="J75" s="1">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" t="s">
-        <v>61</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" s="1">
-        <v>125</v>
-      </c>
-      <c r="D76" s="1">
-        <v>1</v>
-      </c>
-      <c r="E76" s="1">
-        <v>275</v>
-      </c>
-      <c r="F76" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G76" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="H76" s="1">
-        <v>20</v>
-      </c>
-      <c r="I76" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="J76" s="1">
-        <v>21</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="B77" t="s">
-        <v>98</v>
-      </c>
-      <c r="C77" s="1">
-        <v>140</v>
-      </c>
-      <c r="D77" s="1">
-        <v>100</v>
-      </c>
-      <c r="E77" s="1">
-        <v>146</v>
-      </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="I77" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J77" s="1">
-        <v>21</v>
-      </c>
-      <c r="K77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" t="s">
-        <v>59</v>
-      </c>
-      <c r="B78" t="s">
-        <v>99</v>
-      </c>
-      <c r="D78" s="1">
-        <v>100</v>
-      </c>
-      <c r="E78" s="1">
-        <v>553</v>
-      </c>
-      <c r="F78" s="1">
-        <v>28</v>
-      </c>
-      <c r="G78" s="1">
-        <v>20</v>
-      </c>
-      <c r="H78" s="1">
-        <v>42</v>
-      </c>
-      <c r="I78" s="1">
-        <v>3.4</v>
-      </c>
-      <c r="J78" s="1">
-        <v>13</v>
-      </c>
-      <c r="K78" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" t="s">
-        <v>100</v>
-      </c>
-      <c r="B79" t="s">
-        <v>26</v>
-      </c>
-      <c r="D79" s="1">
-        <v>100</v>
-      </c>
-      <c r="E79" s="1">
-        <v>364</v>
-      </c>
-      <c r="F79" s="1">
-        <v>60</v>
-      </c>
-      <c r="G79" s="1">
-        <v>1</v>
-      </c>
-      <c r="H79" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="I79" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J79" s="1">
-        <v>12</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" t="s">
-        <v>101</v>
-      </c>
-      <c r="B80" t="s">
-        <v>102</v>
-      </c>
-      <c r="D80" s="1">
-        <v>100</v>
-      </c>
-      <c r="E80" s="1">
-        <v>608</v>
-      </c>
-      <c r="F80" s="1">
-        <v>12</v>
-      </c>
-      <c r="G80" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="H80" s="1">
-        <v>47</v>
-      </c>
-      <c r="I80" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="J80" s="1">
-        <v>30</v>
-      </c>
-      <c r="K80" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="B81" t="s">
-        <v>103</v>
-      </c>
-      <c r="C81" s="1">
-        <v>125</v>
-      </c>
-      <c r="D81" s="1">
-        <v>100</v>
-      </c>
-      <c r="E81" s="1">
-        <v>192</v>
-      </c>
-      <c r="F81" s="1">
-        <v>11</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H81" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="I81" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="J81" s="1">
-        <v>12.8</v>
-      </c>
-      <c r="K81" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" t="s">
-        <v>104</v>
-      </c>
-      <c r="B82" t="s">
-        <v>105</v>
-      </c>
-      <c r="D82" s="1">
-        <v>100</v>
-      </c>
-      <c r="E82" s="1">
-        <v>421</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>39</v>
-      </c>
-      <c r="I82" s="1">
-        <v>27</v>
-      </c>
-      <c r="J82" s="1">
-        <v>23</v>
-      </c>
-      <c r="K82" s="1">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" t="s">
-        <v>108</v>
-      </c>
-      <c r="B83" t="s">
-        <v>109</v>
-      </c>
-      <c r="D83" s="1">
-        <v>100</v>
-      </c>
-      <c r="E83" s="1">
-        <v>54</v>
-      </c>
-      <c r="F83" s="1">
-        <v>12</v>
-      </c>
-      <c r="G83" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="H83" s="1">
-        <v>0</v>
-      </c>
-      <c r="I83" s="1">
-        <v>0</v>
-      </c>
-      <c r="J83" s="1">
-        <v>0</v>
-      </c>
-      <c r="K83" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" t="s">
-        <v>59</v>
-      </c>
-      <c r="B84" t="s">
-        <v>110</v>
-      </c>
-      <c r="D84" s="1">
-        <v>100</v>
-      </c>
-      <c r="E84" s="1">
-        <v>683</v>
-      </c>
-      <c r="F84" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="G84" s="1">
-        <v>2.9</v>
-      </c>
-      <c r="H84" s="1">
-        <v>66</v>
-      </c>
-      <c r="I84" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J84" s="1">
-        <v>14</v>
-      </c>
-      <c r="K84" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" t="s">
-        <v>59</v>
-      </c>
-      <c r="B85" t="s">
-        <v>111</v>
-      </c>
-      <c r="C85" s="1">
-        <v>150</v>
-      </c>
-      <c r="D85" s="1">
-        <v>100</v>
-      </c>
-      <c r="E85" s="1">
-        <v>54</v>
-      </c>
-      <c r="F85" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G85" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I85" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="J85" s="1">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="K85" s="1">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" t="s">
-        <v>119</v>
-      </c>
-      <c r="C86" s="1">
-        <v>100</v>
-      </c>
-      <c r="D86" s="1">
-        <v>100</v>
-      </c>
-      <c r="E86" s="1">
-        <v>98</v>
-      </c>
-      <c r="F86" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H86" s="1">
-        <v>1</v>
-      </c>
-      <c r="I86" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="J86" s="1">
-        <v>19</v>
-      </c>
-      <c r="K86" s="1">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" t="s">
-        <v>120</v>
-      </c>
-      <c r="C87" s="1">
-        <v>100</v>
-      </c>
-      <c r="D87" s="1">
-        <v>100</v>
-      </c>
-      <c r="E87" s="1">
-        <v>91</v>
-      </c>
-      <c r="F87" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="G87" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="H87" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="I87" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="J87" s="1">
-        <v>17</v>
-      </c>
-      <c r="K87" s="1">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" t="s">
-        <v>121</v>
-      </c>
-      <c r="B88" t="s">
-        <v>122</v>
-      </c>
-      <c r="C88" s="1">
-        <v>300</v>
-      </c>
-      <c r="D88" s="1">
-        <v>100</v>
-      </c>
-      <c r="E88" s="1">
-        <v>134</v>
-      </c>
-      <c r="F88" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H88" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="I88" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J88" s="1">
-        <v>21</v>
-      </c>
-      <c r="K88" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" t="s">
-        <v>59</v>
-      </c>
-      <c r="B89" t="s">
-        <v>123</v>
-      </c>
-      <c r="D89" s="1">
-        <v>100</v>
-      </c>
-      <c r="E89" s="1">
-        <v>67</v>
-      </c>
-      <c r="F89" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G89" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="H89" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="I89" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="J89" s="1">
-        <v>0</v>
-      </c>
-      <c r="K89" s="1">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" t="s">
-        <v>66</v>
-      </c>
-      <c r="B90" t="s">
-        <v>124</v>
-      </c>
-      <c r="C90" s="1">
-        <v>20</v>
-      </c>
-      <c r="D90" s="1">
-        <v>100</v>
-      </c>
-      <c r="E90" s="1">
-        <v>451</v>
-      </c>
-      <c r="F90" s="1">
-        <v>0</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0</v>
-      </c>
-      <c r="H90" s="1">
-        <v>44</v>
-      </c>
-      <c r="I90" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="J90" s="1">
-        <v>13</v>
-      </c>
-      <c r="K90" s="1">
-        <v>9.1</v>
+      <c r="K112" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E6D14F4-4929-AC4B-A15A-0EC8ACFED1EA}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05AC6B74-316C-3E45-8081-01EA56EFF671}"/>
   <bookViews>
     <workbookView xWindow="630" yWindow="840" windowWidth="19575" windowHeight="7080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="181">
   <si>
     <t>kcal</t>
   </si>
@@ -99,9 +99,6 @@
     <t xml:space="preserve">albume </t>
   </si>
   <si>
-    <t>uova</t>
-  </si>
-  <si>
     <t>avena</t>
   </si>
   <si>
@@ -168,15 +165,9 @@
     <t>melone</t>
   </si>
   <si>
-    <t>fragole</t>
-  </si>
-  <si>
     <t>broccolo verde</t>
   </si>
   <si>
-    <t xml:space="preserve">cavolini Bruxelles </t>
-  </si>
-  <si>
     <t>verza</t>
   </si>
   <si>
@@ -351,9 +342,6 @@
     <t>mousse</t>
   </si>
   <si>
-    <t>noci</t>
-  </si>
-  <si>
     <t>skyr</t>
   </si>
   <si>
@@ -465,12 +453,6 @@
     <t>bigMac</t>
   </si>
   <si>
-    <t>patatine fritte</t>
-  </si>
-  <si>
-    <t>nugget</t>
-  </si>
-  <si>
     <t>bigTasty bacon</t>
   </si>
   <si>
@@ -514,6 +496,84 @@
   </si>
   <si>
     <t>supermercati</t>
+  </si>
+  <si>
+    <t>farina integrale</t>
+  </si>
+  <si>
+    <t>pesca</t>
+  </si>
+  <si>
+    <t>cocacola</t>
+  </si>
+  <si>
+    <t>pasticcino alla frutta</t>
+  </si>
+  <si>
+    <t>prosciutto crudo sgrassato</t>
+  </si>
+  <si>
+    <t>vino</t>
+  </si>
+  <si>
+    <t>birra</t>
+  </si>
+  <si>
+    <t>birra analcolica</t>
+  </si>
+  <si>
+    <t>pizza margherita trancio</t>
+  </si>
+  <si>
+    <t>pizza farcita trancio</t>
+  </si>
+  <si>
+    <t>whey protein</t>
+  </si>
+  <si>
+    <t>trota salmonata</t>
+  </si>
+  <si>
+    <t>pesce persico crudo</t>
+  </si>
+  <si>
+    <t>gamberetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philadelphia </t>
+  </si>
+  <si>
+    <t>kraft</t>
+  </si>
+  <si>
+    <t>pasticceria</t>
+  </si>
+  <si>
+    <t>uovo</t>
+  </si>
+  <si>
+    <t>cotoletta light</t>
+  </si>
+  <si>
+    <t>nugget x6</t>
+  </si>
+  <si>
+    <t>patatine fritte piccolo</t>
+  </si>
+  <si>
+    <t>pinoli</t>
+  </si>
+  <si>
+    <t>mandorle sgusciate x10</t>
+  </si>
+  <si>
+    <t>fragola</t>
+  </si>
+  <si>
+    <t>cavolini Bruxelles 1 pezzo</t>
+  </si>
+  <si>
+    <t>noci x9</t>
   </si>
 </sst>
 </file>
@@ -895,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.46875" customWidth="1"/>
@@ -907,22 +967,22 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -931,7 +991,7 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
@@ -942,7 +1002,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -977,10 +1037,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="C3" s="1">
+        <v>80</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
@@ -1008,151 +1071,157 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
       <c r="B4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="1">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1">
+        <v>100</v>
+      </c>
+      <c r="E4" s="1">
+        <v>332</v>
+      </c>
+      <c r="F4" s="1">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="J4" s="1">
+        <v>13</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1">
-        <v>100</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
+        <v>100</v>
+      </c>
+      <c r="E5" s="1">
         <v>900</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>100</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="1">
         <v>14</v>
       </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="1">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1">
-        <v>100</v>
-      </c>
-      <c r="E5" s="1">
-        <v>112</v>
-      </c>
-      <c r="F5" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="G5" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6</v>
-      </c>
-      <c r="I5" s="1">
-        <v>4.0999999999999996</v>
-      </c>
       <c r="J5" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>56</v>
+      </c>
+      <c r="C6" s="1">
+        <v>90</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="F6" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>6</v>
+      </c>
+      <c r="I6" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J6" s="1">
+        <v>9</v>
+      </c>
+      <c r="K6" s="1">
         <v>0.5</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="J6" s="1">
-        <v>34</v>
-      </c>
-      <c r="K6" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K7" s="1">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1161,48 +1230,48 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="I8" s="1">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1">
+        <v>90</v>
+      </c>
+      <c r="D9" s="1">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1">
+        <v>119</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="J9" s="1">
         <v>23</v>
-      </c>
-      <c r="D9" s="1">
-        <v>100</v>
-      </c>
-      <c r="E9" s="1">
-        <v>275</v>
-      </c>
-      <c r="F9" s="1">
-        <v>38</v>
-      </c>
-      <c r="G9" s="1">
-        <v>7</v>
-      </c>
-      <c r="H9" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="J9" s="1">
-        <v>11</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
@@ -1210,63 +1279,69 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1">
-        <v>349</v>
+        <v>275</v>
       </c>
       <c r="F10" s="1">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1">
+        <v>7</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="I10" s="1">
         <v>0.6</v>
       </c>
-      <c r="H10" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.3</v>
-      </c>
       <c r="J10" s="1">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>62</v>
+      </c>
+      <c r="C11" s="1">
+        <v>70</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F11" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H11" s="1">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J11" s="1">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -1274,45 +1349,45 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="F12" s="1">
-        <v>12.1</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="K12" s="1">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="C13" s="1">
         <v>140</v>
@@ -1321,22 +1396,22 @@
         <v>100</v>
       </c>
       <c r="E13" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F13" s="1">
-        <v>14.5</v>
+        <v>12.1</v>
       </c>
       <c r="G13" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H13" s="1">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I13" s="1">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J13" s="1">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1">
         <v>1.1000000000000001</v>
@@ -1344,10 +1419,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1">
         <v>140</v>
@@ -1356,33 +1431,33 @@
         <v>100</v>
       </c>
       <c r="E14" s="1">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F14" s="1">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I14" s="1">
         <v>0.1</v>
       </c>
       <c r="J14" s="1">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="K14" s="1">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1">
         <v>140</v>
@@ -1391,33 +1466,33 @@
         <v>100</v>
       </c>
       <c r="E15" s="1">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F15" s="1">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="G15" s="1">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="1">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="1">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J15" s="1">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1">
         <v>140</v>
@@ -1426,33 +1501,33 @@
         <v>100</v>
       </c>
       <c r="E16" s="1">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="F16" s="1">
-        <v>11</v>
+        <v>15.8</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H16" s="1">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="I16" s="1">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="1">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="K16" s="1">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>140</v>
@@ -1461,24 +1536,36 @@
         <v>100</v>
       </c>
       <c r="E17" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.1</v>
       </c>
       <c r="J17" s="1">
-        <v>4.7</v>
+        <v>7.2</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.7</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1">
         <v>140</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
@@ -1487,62 +1574,53 @@
         <v>96</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1">
         <v>0.6</v>
       </c>
-      <c r="I18" s="1">
-        <v>0.2</v>
-      </c>
       <c r="J18" s="1">
-        <v>22</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F19" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I19" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J19" s="1">
-        <v>18</v>
-      </c>
-      <c r="K19" s="1">
-        <v>1.8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>100</v>
@@ -1551,33 +1629,33 @@
         <v>100</v>
       </c>
       <c r="E20" s="1">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="1">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="1">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J20" s="1">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K20" s="1">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C21" s="1">
         <v>100</v>
@@ -1586,33 +1664,33 @@
         <v>100</v>
       </c>
       <c r="E21" s="1">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="F21" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>24</v>
+      </c>
+      <c r="K21" s="1">
         <v>0.1</v>
-      </c>
-      <c r="H21" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="J21" s="1">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1.8</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1">
         <v>100</v>
@@ -1621,333 +1699,354 @@
         <v>100</v>
       </c>
       <c r="E22" s="1">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="F22" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G22" s="1">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H22" s="1">
-        <v>16</v>
+        <v>8.5</v>
       </c>
       <c r="I22" s="1">
-        <v>6.2</v>
+        <v>0.1</v>
       </c>
       <c r="J22" s="1">
-        <v>30</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="K22" s="1">
-        <v>4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C23" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="F23" s="1">
-        <v>28</v>
+        <v>0.5</v>
       </c>
       <c r="G23" s="1">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H23" s="1">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J23" s="1">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K23" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C24" s="1">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F24" s="1">
-        <v>31.7</v>
+        <v>28</v>
       </c>
       <c r="G24" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="H24" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="I24" s="1">
         <v>3.8</v>
       </c>
-      <c r="H24" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="I24" s="1">
-        <v>3.3</v>
-      </c>
       <c r="J24" s="1">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="K24" s="1">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="C25" s="1">
-        <v>125</v>
+        <v>330</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>31.7</v>
       </c>
       <c r="G25" s="1">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="H25" s="1">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="I25" s="1">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="J25" s="1">
-        <v>17</v>
+        <v>10.3</v>
       </c>
       <c r="K25" s="1">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>20</v>
+      </c>
+      <c r="C26" s="1">
+        <v>125</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="F26" s="1">
-        <v>8.8000000000000007</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="H26" s="1">
-        <v>0.4</v>
+        <v>11</v>
       </c>
       <c r="I26" s="1">
-        <v>0.1</v>
+        <v>7.1</v>
       </c>
       <c r="J26" s="1">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="K26" s="1">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="1">
+        <v>90</v>
+      </c>
+      <c r="D27" s="1">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1">
+        <v>71</v>
+      </c>
+      <c r="F27" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G27" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="1">
-        <v>100</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="C28" s="1">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1">
         <v>47</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F28" s="1">
         <v>0.8</v>
       </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
         <v>11</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K28" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="1">
-        <v>100</v>
-      </c>
-      <c r="E28" s="1">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="1">
+        <v>55</v>
+      </c>
+      <c r="D29" s="1">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1">
         <v>128</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
         <v>8.6999999999999993</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I29" s="1">
         <v>3.2</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J29" s="1">
         <v>12.4</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K29" s="1">
         <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="1">
-        <v>100</v>
-      </c>
-      <c r="E29" s="1">
-        <v>403</v>
-      </c>
-      <c r="F29" s="1">
-        <v>59</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H29" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="J29" s="1">
-        <v>21</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="F30" s="1">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G30" s="1">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="1">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="I30" s="1">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J30" s="1">
         <v>21</v>
       </c>
       <c r="K30" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>24</v>
+      </c>
+      <c r="C31" s="1">
+        <v>30</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1">
-        <v>76</v>
+        <v>383</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H31" s="1">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="I31" s="1">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J31" s="1">
-        <v>17.2</v>
+        <v>21</v>
       </c>
       <c r="K31" s="1">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C32" s="1">
+        <v>100</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -1956,126 +2055,129 @@
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I32" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J32" s="1">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="K32" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="C33" s="1">
+        <v>100</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1">
+        <v>71</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="1">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1">
+        <v>100</v>
+      </c>
+      <c r="E34" s="1">
         <v>295</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F34" s="1">
         <v>0.5</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G34" s="1">
         <v>0.5</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H34" s="1">
         <v>23</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I34" s="1">
         <v>15.5</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J34" s="1">
         <v>22</v>
       </c>
-      <c r="K33" s="1">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="1">
-        <v>75</v>
-      </c>
-      <c r="D35" s="1">
-        <v>100</v>
-      </c>
-      <c r="E35" s="1">
-        <v>130</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I35" s="1">
-        <v>2</v>
-      </c>
-      <c r="J35" s="1">
-        <v>21</v>
-      </c>
-      <c r="K35" s="1">
+      <c r="K34" s="1">
         <v>1.7</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F36" s="1">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0.8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I36" s="1">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J36" s="1">
-        <v>4.4000000000000004</v>
+        <v>21</v>
       </c>
       <c r="K36" s="1">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C37" s="1">
         <v>140</v>
@@ -2084,86 +2186,92 @@
         <v>100</v>
       </c>
       <c r="E37" s="1">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F37" s="1">
-        <v>17.899999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="G37" s="1">
-        <v>4.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="I37" s="1">
         <v>0.2</v>
       </c>
       <c r="J37" s="1">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="K37" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="C38" s="1">
+        <v>140</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1">
-        <v>376</v>
+        <v>115</v>
       </c>
       <c r="F38" s="1">
-        <v>69.3</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="G38" s="1">
-        <v>0.8</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H38" s="1">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="I38" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="K38" s="1">
         <v>0.4</v>
-      </c>
-      <c r="J38" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>28</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1">
-        <v>47</v>
+        <v>376</v>
       </c>
       <c r="F39" s="1">
-        <v>4.9000000000000004</v>
+        <v>69.3</v>
       </c>
       <c r="G39" s="1">
-        <v>4.9000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="H39" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="I39" s="1">
-        <v>1.1000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J39" s="1">
-        <v>3.2</v>
+        <v>13.8</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -2171,391 +2279,418 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>104</v>
+      </c>
+      <c r="C40" s="1">
+        <v>100</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="F40" s="1">
-        <v>31</v>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G40" s="1">
+        <v>4.9000000000000004</v>
       </c>
       <c r="H40" s="1">
-        <v>0.8</v>
+        <v>1.6</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1.1000000000000001</v>
       </c>
       <c r="J40" s="1">
-        <v>4.4000000000000004</v>
+        <v>3.2</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="1">
+        <v>125</v>
+      </c>
+      <c r="D41" s="1">
+        <v>100</v>
+      </c>
+      <c r="E41" s="1">
+        <v>151</v>
+      </c>
+      <c r="F41" s="1">
         <v>31</v>
       </c>
-      <c r="D41" s="1">
-        <v>100</v>
-      </c>
-      <c r="E41" s="1">
-        <v>253</v>
-      </c>
-      <c r="F41" s="1">
-        <v>55.4</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.5</v>
-      </c>
       <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J41" s="1">
-        <v>9</v>
-      </c>
-      <c r="K41" s="1">
-        <v>1.6</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="C42" s="1">
+        <v>70</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1">
-        <v>30</v>
+        <v>253</v>
       </c>
       <c r="F42" s="1">
-        <v>4.9000000000000004</v>
+        <v>55.4</v>
       </c>
       <c r="G42" s="1">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="H42" s="1">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I42" s="1">
         <v>0.1</v>
       </c>
       <c r="J42" s="1">
+        <v>9</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="1">
+        <v>100</v>
+      </c>
+      <c r="D43" s="1">
+        <v>100</v>
+      </c>
+      <c r="E43" s="1">
+        <v>30</v>
+      </c>
+      <c r="F43" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G43" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J43" s="1">
         <v>1.2</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K43" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>158</v>
-      </c>
-      <c r="D43" s="1">
-        <v>100</v>
-      </c>
-      <c r="E43" s="1">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" s="1">
+        <v>20</v>
+      </c>
+      <c r="D44" s="1">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1">
         <v>129</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
         <v>13</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I44" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J44" s="1">
         <v>0.5</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K44" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="1">
-        <v>30</v>
-      </c>
-      <c r="D44" s="1">
-        <v>100</v>
-      </c>
-      <c r="E44" s="1">
-        <v>337</v>
-      </c>
-      <c r="F44" s="1">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1">
-        <v>29</v>
-      </c>
-      <c r="I44" s="1">
-        <v>19</v>
-      </c>
-      <c r="J44" s="1">
-        <v>19</v>
-      </c>
-      <c r="K44" s="1">
-        <v>1.5</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C45" s="1">
+        <v>30</v>
+      </c>
+      <c r="D45" s="1">
+        <v>100</v>
+      </c>
+      <c r="E45" s="1">
+        <v>337</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>29</v>
+      </c>
+      <c r="I45" s="1">
+        <v>19</v>
+      </c>
+      <c r="J45" s="1">
+        <v>19</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" s="1">
         <v>150</v>
       </c>
-      <c r="D45" s="1">
-        <v>100</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D46" s="1">
+        <v>100</v>
+      </c>
+      <c r="E46" s="1">
         <v>108</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F46" s="1">
         <v>14</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G46" s="1">
         <v>14</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H46" s="1">
         <v>3.6</v>
       </c>
-      <c r="I45" s="1">
+      <c r="I46" s="1">
         <v>2.4</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J46" s="1">
         <v>3.7</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K46" s="1">
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="1">
-        <v>100</v>
-      </c>
-      <c r="E46" s="1">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="1">
+        <v>280</v>
+      </c>
+      <c r="D47" s="1">
+        <v>100</v>
+      </c>
+      <c r="E47" s="1">
         <v>72</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F47" s="1">
         <v>16</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G47" s="1">
         <v>1</v>
       </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
         <v>2</v>
       </c>
-      <c r="K46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="1">
-        <v>100</v>
-      </c>
-      <c r="E47" s="1">
-        <v>162</v>
-      </c>
-      <c r="F47" s="1">
-        <v>24</v>
-      </c>
-      <c r="H47" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="J47" s="1">
-        <v>3</v>
+      <c r="K47" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>33</v>
+      </c>
+      <c r="C48" s="1">
+        <v>100</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1">
-        <v>350</v>
+        <v>162</v>
       </c>
       <c r="F48" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="G48" s="1">
-        <v>3.8</v>
+        <v>24</v>
       </c>
       <c r="H48" s="1">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="I48" s="1">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J48" s="1">
-        <v>3.7</v>
-      </c>
-      <c r="K48" s="1">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>83</v>
+      </c>
+      <c r="C49" s="1">
+        <v>20</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1">
-        <v>96</v>
+        <v>350</v>
       </c>
       <c r="F49" s="1">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="G49" s="1">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H49" s="1">
-        <v>4.5999999999999996</v>
+        <v>34</v>
       </c>
       <c r="I49" s="1">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J49" s="1">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="K49" s="1">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>146</v>
+      </c>
+      <c r="C50" s="1">
+        <v>170</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F50" s="1">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="G50" s="1">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="H50" s="1">
-        <v>6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I50" s="1">
-        <v>4.4000000000000004</v>
+        <v>3.3</v>
       </c>
       <c r="J50" s="1">
         <v>10</v>
       </c>
       <c r="K50" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="C51" s="1">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="1">
+        <v>6</v>
+      </c>
+      <c r="I51" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
+        <v>10</v>
+      </c>
+      <c r="K51" s="1">
         <v>0.8</v>
-      </c>
-      <c r="J51" s="1">
-        <v>20.5</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0.1</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C52" s="1">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -2564,13 +2699,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>6.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I52" s="1">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J52" s="1">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="K52" s="1">
         <v>0.1</v>
@@ -2578,330 +2713,375 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>106</v>
+      </c>
+      <c r="C53" s="1">
+        <v>190</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="F53" s="1">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="I53" s="1">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J53" s="1">
-        <v>9.9</v>
+        <v>19.7</v>
       </c>
       <c r="K53" s="1">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>34</v>
+      </c>
+      <c r="C54" s="1">
+        <v>130</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="F54" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H54" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="I54" s="1">
         <v>0.8</v>
       </c>
-      <c r="G54" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H54" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I54" s="1">
-        <v>0.1</v>
-      </c>
       <c r="J54" s="1">
-        <v>20</v>
+        <v>9.9</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="B55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="1">
+        <v>100</v>
+      </c>
+      <c r="D55" s="1">
+        <v>100</v>
+      </c>
+      <c r="E55" s="1">
+        <v>86</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J55" s="1">
+        <v>20</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="1">
+        <v>20</v>
+      </c>
+      <c r="D56" s="1">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1">
+        <v>241</v>
+      </c>
+      <c r="F56" s="1">
+        <v>59</v>
+      </c>
+      <c r="G56" s="1">
+        <v>56</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>36</v>
       </c>
-      <c r="D55" s="1">
-        <v>100</v>
-      </c>
-      <c r="E55" s="1">
-        <v>241</v>
-      </c>
-      <c r="F55" s="1">
-        <v>59</v>
-      </c>
-      <c r="G55" s="1">
-        <v>56</v>
-      </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
-      <c r="J55" s="1">
+      <c r="C57" s="1">
+        <v>25</v>
+      </c>
+      <c r="D57" s="1">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1">
+        <v>65</v>
+      </c>
+      <c r="F57" s="1">
         <v>0.5</v>
       </c>
-      <c r="K55" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>37</v>
-      </c>
-      <c r="D56" s="1">
-        <v>100</v>
-      </c>
-      <c r="E56" s="1">
-        <v>65</v>
-      </c>
-      <c r="F56" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
-      </c>
-      <c r="H56" s="1">
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
         <v>0.6</v>
       </c>
-      <c r="I56" s="1">
+      <c r="I57" s="1">
         <v>0.2</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J57" s="1">
         <v>14.2</v>
       </c>
-      <c r="K56" s="1">
+      <c r="K57" s="1">
         <v>1.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>149</v>
-      </c>
-      <c r="B57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" s="1">
-        <v>60</v>
-      </c>
-      <c r="D57" s="1">
-        <v>100</v>
-      </c>
-      <c r="E57" s="1">
-        <v>245</v>
-      </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
-      </c>
-      <c r="H57" s="1">
-        <v>17</v>
-      </c>
-      <c r="I57" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J57" s="1">
-        <v>23</v>
-      </c>
-      <c r="K57" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="C58" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
         <v>17</v>
       </c>
-      <c r="G58" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H58" s="1">
-        <v>12</v>
-      </c>
       <c r="I58" s="1">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="J58" s="1">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K58" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" s="1">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F59" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G59" s="1">
         <v>0.6</v>
       </c>
       <c r="H59" s="1">
+        <v>12</v>
+      </c>
+      <c r="I59" s="1">
+        <v>12</v>
+      </c>
+      <c r="J59" s="1">
+        <v>12</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" s="1">
+        <v>125</v>
+      </c>
+      <c r="D60" s="1">
+        <v>100</v>
+      </c>
+      <c r="E60" s="1">
+        <v>225</v>
+      </c>
+      <c r="F60" s="1">
+        <v>12</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H60" s="1">
         <v>13</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I60" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J60" s="1">
         <v>15</v>
       </c>
-      <c r="K59" s="1">
+      <c r="K60" s="1">
         <v>1.3</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" t="s">
+    <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="1">
-        <v>100</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="1">
+        <v>100</v>
+      </c>
+      <c r="E61" s="1">
         <v>104</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F61" s="1">
         <v>4.2</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G61" s="1">
         <v>3.5</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H61" s="1">
         <v>1.7</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I61" s="1">
         <v>0.3</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J61" s="1">
         <v>17.100000000000001</v>
       </c>
-      <c r="K60" s="1">
+      <c r="K61" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61" s="1">
-        <v>70</v>
-      </c>
-      <c r="D61" s="1">
-        <v>100</v>
-      </c>
-      <c r="E61" s="1">
-        <v>61</v>
-      </c>
-      <c r="F61" s="1">
-        <v>14.7</v>
-      </c>
-      <c r="G61" s="1">
-        <v>9</v>
-      </c>
-      <c r="H61" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="C62" s="1">
+        <v>70</v>
+      </c>
+      <c r="D62" s="1">
+        <v>100</v>
+      </c>
+      <c r="E62" s="1">
+        <v>61</v>
+      </c>
+      <c r="F62" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="G62" s="1">
+        <v>9</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C63" s="1">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="F63" s="1">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="G63" s="1">
-        <v>17.3</v>
+        <v>9.4</v>
       </c>
       <c r="H63" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -2909,22 +3089,22 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C64" s="1">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="F64" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G64" s="1">
-        <v>10.4</v>
+        <v>17.3</v>
       </c>
       <c r="H64" s="1">
         <v>0.2</v>
@@ -2933,27 +3113,30 @@
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="C65" s="1">
+        <v>180</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F65" s="1">
-        <v>8.1999999999999993</v>
+        <v>14</v>
       </c>
       <c r="G65" s="1">
-        <v>7.9</v>
+        <v>10.4</v>
       </c>
       <c r="H65" s="1">
         <v>0.2</v>
@@ -2962,94 +3145,94 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" s="1">
+        <v>100</v>
+      </c>
+      <c r="D66" s="1">
+        <v>100</v>
+      </c>
+      <c r="E66" s="1">
+        <v>34</v>
+      </c>
+      <c r="F66" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G66" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
         <v>0.8</v>
       </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
-        <v>148</v>
-      </c>
-      <c r="C66" s="1">
-        <v>100</v>
-      </c>
-      <c r="D66" s="1">
-        <v>100</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="1">
+        <v>100</v>
+      </c>
+      <c r="D67" s="1">
+        <v>100</v>
+      </c>
+      <c r="E67" s="1">
         <v>37</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F67" s="1">
         <v>7.2</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G67" s="1">
         <v>2.4</v>
       </c>
-      <c r="H66" s="1">
+      <c r="H67" s="1">
         <v>0.4</v>
       </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>45</v>
-      </c>
-      <c r="C67" s="1">
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="1">
         <v>12</v>
       </c>
-      <c r="D67" s="1">
-        <v>100</v>
-      </c>
-      <c r="E67" s="1">
+      <c r="D68" s="1">
+        <v>100</v>
+      </c>
+      <c r="E68" s="1">
         <v>32</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F68" s="1">
         <v>7.7</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G68" s="1">
         <v>4.9000000000000004</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I67" s="1">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B68" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="1">
-        <v>150</v>
-      </c>
-      <c r="D68" s="1">
-        <v>100</v>
-      </c>
-      <c r="E68" s="1">
-        <v>25</v>
-      </c>
-      <c r="F68" s="1">
-        <v>5</v>
-      </c>
-      <c r="G68" s="1">
-        <v>2</v>
       </c>
       <c r="H68" s="1">
         <v>0.3</v>
@@ -3058,15 +3241,15 @@
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C69" s="1">
         <v>150</v>
@@ -3075,364 +3258,511 @@
         <v>100</v>
       </c>
       <c r="E69" s="1">
+        <v>25</v>
+      </c>
+      <c r="F69" s="1">
+        <v>5</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="1">
+        <v>240</v>
+      </c>
+      <c r="D70" s="1">
+        <v>100</v>
+      </c>
+      <c r="E70" s="1">
+        <v>44</v>
+      </c>
+      <c r="F70" s="1">
+        <v>10</v>
+      </c>
+      <c r="G70" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>127</v>
+      </c>
+      <c r="C71" s="1">
+        <v>150</v>
+      </c>
+      <c r="D71" s="1">
+        <v>100</v>
+      </c>
+      <c r="E71" s="1">
         <v>69</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F71" s="1">
         <v>18</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G71" s="1">
         <v>15</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H71" s="1">
         <v>0.2</v>
       </c>
-      <c r="I69" s="1">
-        <v>0</v>
-      </c>
-      <c r="J69" s="1">
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
         <v>0.7</v>
       </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72" s="1">
+        <v>150</v>
+      </c>
+      <c r="D72" s="1">
+        <v>100</v>
+      </c>
+      <c r="E72" s="1">
+        <v>34</v>
+      </c>
+      <c r="F72" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>179</v>
+      </c>
+      <c r="C73" s="1">
+        <v>21</v>
+      </c>
+      <c r="D73" s="1">
+        <v>100</v>
+      </c>
+      <c r="E73" s="1">
+        <v>36</v>
+      </c>
+      <c r="F73" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1">
+        <v>250</v>
+      </c>
+      <c r="D74" s="1">
+        <v>100</v>
+      </c>
+      <c r="E74" s="1">
+        <v>27</v>
+      </c>
+      <c r="F74" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <v>2</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
+      <c r="C75" s="1">
+        <v>200</v>
+      </c>
+      <c r="D75" s="1">
+        <v>100</v>
+      </c>
+      <c r="E75" s="1">
+        <v>34</v>
+      </c>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <v>3</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
         <v>47</v>
       </c>
-      <c r="C71" s="1">
-        <v>21</v>
-      </c>
-      <c r="D71" s="1">
-        <v>100</v>
-      </c>
-      <c r="E71" s="1">
-        <v>36</v>
-      </c>
-      <c r="F71" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="G71" s="1">
+      <c r="C76" s="1">
+        <v>130</v>
+      </c>
+      <c r="D76" s="1">
+        <v>100</v>
+      </c>
+      <c r="E76" s="1">
+        <v>41</v>
+      </c>
+      <c r="F76" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="1">
+        <v>250</v>
+      </c>
+      <c r="D77" s="1">
+        <v>100</v>
+      </c>
+      <c r="E77" s="1">
+        <v>15</v>
+      </c>
+      <c r="F77" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G77" s="1">
         <v>1.7</v>
       </c>
-      <c r="H71" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I71" s="1">
-        <v>0</v>
-      </c>
-      <c r="J71" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B73" t="s">
+      <c r="H77" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>109</v>
+      </c>
+      <c r="C78" s="1">
+        <v>260</v>
+      </c>
+      <c r="D78" s="1">
+        <v>100</v>
+      </c>
+      <c r="E78" s="1">
+        <v>17</v>
+      </c>
+      <c r="F78" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
         <v>49</v>
       </c>
-      <c r="D73" s="1">
-        <v>100</v>
-      </c>
-      <c r="E73" s="1">
-        <v>34</v>
-      </c>
-      <c r="F73" s="1">
+      <c r="C79" s="1">
+        <v>100</v>
+      </c>
+      <c r="D79" s="1">
+        <v>100</v>
+      </c>
+      <c r="E79" s="1">
+        <v>26</v>
+      </c>
+      <c r="F79" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="1">
+        <v>250</v>
+      </c>
+      <c r="D80" s="1">
+        <v>100</v>
+      </c>
+      <c r="E80" s="1">
+        <v>73</v>
+      </c>
+      <c r="F80" s="1">
+        <v>17</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1">
         <v>3</v>
       </c>
-      <c r="G73" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="H73" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I73" s="1">
-        <v>0</v>
-      </c>
-      <c r="J73" s="1">
+      <c r="K80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" s="1">
+        <v>100</v>
+      </c>
+      <c r="D81" s="1">
+        <v>100</v>
+      </c>
+      <c r="E81" s="1">
+        <v>25</v>
+      </c>
+      <c r="F81" s="1">
+        <v>6</v>
+      </c>
+      <c r="G81" s="1">
         <v>3</v>
       </c>
-      <c r="K73" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B74" t="s">
-        <v>50</v>
-      </c>
-      <c r="C74" s="1">
-        <v>130</v>
-      </c>
-      <c r="D74" s="1">
-        <v>100</v>
-      </c>
-      <c r="E74" s="1">
-        <v>41</v>
-      </c>
-      <c r="F74" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="G74" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="H74" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I74" s="1">
-        <v>0</v>
-      </c>
-      <c r="J74" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="K74" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B75" t="s">
-        <v>51</v>
-      </c>
-      <c r="C75" s="1">
-        <v>250</v>
-      </c>
-      <c r="D75" s="1">
-        <v>100</v>
-      </c>
-      <c r="E75" s="1">
-        <v>15</v>
-      </c>
-      <c r="F75" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="G75" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="H75" s="1">
+      <c r="H81" s="1">
         <v>0.1</v>
       </c>
-      <c r="I75" s="1">
-        <v>0</v>
-      </c>
-      <c r="J75" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K75" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="1">
-        <v>260</v>
-      </c>
-      <c r="D76" s="1">
-        <v>100</v>
-      </c>
-      <c r="E76" s="1">
-        <v>17</v>
-      </c>
-      <c r="F76" s="1">
-        <v>3.1</v>
-      </c>
-      <c r="G76" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H76" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I76" s="1">
-        <v>0</v>
-      </c>
-      <c r="J76" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B77" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B78" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" t="s">
-        <v>92</v>
-      </c>
-      <c r="C80" s="1">
-        <v>125</v>
-      </c>
-      <c r="D80" s="1">
-        <v>1</v>
-      </c>
-      <c r="E80" s="1">
-        <v>140</v>
-      </c>
-      <c r="F80" s="1">
-        <v>18.8</v>
-      </c>
-      <c r="H80" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="J80" s="1">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>58</v>
-      </c>
-      <c r="B81" t="s">
-        <v>93</v>
-      </c>
-      <c r="C81" s="1">
-        <v>125</v>
-      </c>
-      <c r="D81" s="1">
-        <v>1</v>
-      </c>
-      <c r="E81" s="1">
-        <v>275</v>
-      </c>
-      <c r="F81" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G81" s="1">
+      <c r="I81" s="1">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1">
         <v>1.3</v>
       </c>
-      <c r="H81" s="1">
-        <v>20</v>
-      </c>
-      <c r="I81" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="J81" s="1">
-        <v>21</v>
-      </c>
       <c r="K81" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="1">
+        <v>125</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1">
         <v>140</v>
       </c>
-      <c r="B82" t="s">
-        <v>94</v>
-      </c>
-      <c r="C82" s="1">
-        <v>140</v>
-      </c>
-      <c r="D82" s="1">
-        <v>100</v>
-      </c>
-      <c r="E82" s="1">
-        <v>146</v>
-      </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H82" s="1">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="I82" s="1">
-        <v>2.2000000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="J82" s="1">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K82" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>90</v>
+      </c>
+      <c r="C83" s="1">
+        <v>125</v>
       </c>
       <c r="D83" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E83" s="1">
-        <v>553</v>
+        <v>275</v>
       </c>
       <c r="F83" s="1">
-        <v>28</v>
+        <v>2.5</v>
       </c>
       <c r="G83" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="H83" s="1">
         <v>20</v>
       </c>
-      <c r="H83" s="1">
-        <v>42</v>
-      </c>
       <c r="I83" s="1">
-        <v>3.4</v>
+        <v>13.8</v>
       </c>
       <c r="J83" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K83" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>91</v>
+      </c>
+      <c r="C84" s="1">
+        <v>140</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1">
-        <v>364</v>
+        <v>146</v>
       </c>
       <c r="F84" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="1">
         <v>6.2</v>
       </c>
       <c r="I84" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J84" s="1">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
@@ -3440,31 +3770,34 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="C85" s="1">
+        <v>30</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1">
-        <v>608</v>
+        <v>553</v>
       </c>
       <c r="F85" s="1">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G85" s="1">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="H85" s="1">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I85" s="1">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J85" s="1">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
@@ -3472,144 +3805,153 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="C86" s="1">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="F86" s="1">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G86" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H86" s="1">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="I86" s="1">
-        <v>0.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J86" s="1">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="K86" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="C87" s="1">
+        <v>15</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1">
-        <v>421</v>
+        <v>608</v>
       </c>
       <c r="F87" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G87" s="1">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H87" s="1">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I87" s="1">
-        <v>27</v>
+        <v>6.6</v>
       </c>
       <c r="J87" s="1">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K87" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="B88" t="s">
-        <v>105</v>
+        <v>96</v>
+      </c>
+      <c r="C88" s="1">
+        <v>125</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="F88" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G88" s="1">
-        <v>9.5</v>
+        <v>0.2</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I88" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J88" s="1">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="K88" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="C89" s="1">
+        <v>30</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1">
-        <v>683</v>
+        <v>421</v>
       </c>
       <c r="F89" s="1">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I89" s="1">
-        <v>5.0999999999999996</v>
+        <v>27</v>
       </c>
       <c r="J89" s="1">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K89" s="1">
-        <v>0.01</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C90" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
@@ -3618,156 +3960,159 @@
         <v>54</v>
       </c>
       <c r="F90" s="1">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="G90" s="1">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="H90" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I90" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>9.1999999999999993</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="B91" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="C91" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1">
-        <v>98</v>
+        <v>683</v>
       </c>
       <c r="F91" s="1">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="G91" s="1">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="H91" s="1">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="I91" s="1">
-        <v>0.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J91" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K91" s="1">
-        <v>2.1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="B92" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C92" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="F92" s="1">
-        <v>4.0999999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="G92" s="1">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="H92" s="1">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="I92" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J92" s="1">
-        <v>17</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K92" s="1">
-        <v>1.9</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B93" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C93" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="F93" s="1">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="G93" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H93" s="1">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="I93" s="1">
-        <v>2.2000000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="J93" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K93" s="1">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="B94" t="s">
-        <v>119</v>
+        <v>112</v>
+      </c>
+      <c r="C94" s="1">
+        <v>100</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F94" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G94" s="1">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="H94" s="1">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="I94" s="1">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J94" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K94" s="1">
         <v>1.9</v>
@@ -3775,325 +4120,325 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B95" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C95" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1">
-        <v>451</v>
+        <v>134</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H95" s="1">
-        <v>44</v>
+        <v>5.5</v>
       </c>
       <c r="I95" s="1">
-        <v>5.7</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J95" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K95" s="1">
-        <v>9.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C96" s="1">
         <v>70</v>
       </c>
       <c r="D96" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E96" s="1">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F96" s="1">
-        <v>34</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G96" s="1">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="H96" s="1">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="I96" s="1">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J96" s="1">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C97" s="1">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="D97" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E97" s="1">
-        <v>330</v>
+        <v>451</v>
       </c>
       <c r="F97" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G97" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I97" s="1">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="J97" s="1">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="K97" s="1">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B98" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C98" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D98" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E98" s="1">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="F98" s="1">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G98" s="1">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H98" s="1">
-        <v>0.8</v>
+        <v>16</v>
       </c>
       <c r="I98" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J98" s="1">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="K98" s="1">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>56</v>
+      <c r="A99" t="s">
+        <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C99" s="1">
         <v>75</v>
       </c>
       <c r="D99" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E99" s="1">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="F99" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G99" s="1">
-        <v>4.5999999999999996</v>
+        <v>15</v>
       </c>
       <c r="H99" s="1">
+        <v>17</v>
+      </c>
+      <c r="I99" s="1">
+        <v>8</v>
+      </c>
+      <c r="J99" s="1">
         <v>5.5</v>
       </c>
-      <c r="I99" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="J99" s="1">
-        <v>11</v>
-      </c>
       <c r="K99" s="1">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B100" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C100" s="1">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="F100" s="1">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G100" s="1">
-        <v>0.3</v>
+        <v>23</v>
       </c>
       <c r="H100" s="1">
-        <v>8.3000000000000007</v>
+        <v>0.8</v>
       </c>
       <c r="I100" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J100" s="1">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="K100" s="1">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>132</v>
+      <c r="A101" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B101" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C101" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="F101" s="1">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="G101" s="1">
-        <v>0.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H101" s="1">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="I101" s="1">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J101" s="1">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K101" s="1">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B102" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C102" s="1">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1">
-        <v>544</v>
+        <v>313</v>
       </c>
       <c r="F102" s="1">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G102" s="1">
-        <v>51</v>
+        <v>0.3</v>
       </c>
       <c r="H102" s="1">
-        <v>32</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I102" s="1">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J102" s="1">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="K102" s="1">
-        <v>0.12</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C103" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="F103" s="1">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G103" s="1">
-        <v>26</v>
+        <v>0.7</v>
       </c>
       <c r="H103" s="1">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I103" s="1">
-        <v>9.6999999999999993</v>
+        <v>7.6</v>
       </c>
       <c r="J103" s="1">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K103" s="1">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B104" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C104" s="1">
         <v>15</v>
@@ -4102,162 +4447,162 @@
         <v>100</v>
       </c>
       <c r="E104" s="1">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F104" s="1">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G104" s="1">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H104" s="1">
-        <v>30.9</v>
+        <v>32</v>
       </c>
       <c r="I104" s="1">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="J104" s="1">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="K104" s="1">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B105" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C105" s="1">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="F105" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H105" s="1">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="I105" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="J105" s="1">
         <v>3</v>
       </c>
-      <c r="J105" s="1">
-        <v>23</v>
-      </c>
       <c r="K105" s="1">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B106" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C106" s="1">
-        <v>230</v>
+        <v>15</v>
       </c>
       <c r="D106" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E106" s="1">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="F106" s="1">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G106" s="1">
-        <v>8.6</v>
+        <v>56</v>
       </c>
       <c r="H106" s="1">
-        <v>27</v>
+        <v>30.9</v>
       </c>
       <c r="I106" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J106" s="1">
-        <v>27</v>
+        <v>6.3</v>
       </c>
       <c r="K106" s="1">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B107" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C107" s="1">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="D107" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E107" s="1">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="F107" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="I107" s="1">
+        <v>3</v>
+      </c>
+      <c r="J107" s="1">
+        <v>23</v>
+      </c>
+      <c r="K107" s="1">
         <v>0.1</v>
-      </c>
-      <c r="H107" s="1">
-        <v>11</v>
-      </c>
-      <c r="I107" s="1">
-        <v>2</v>
-      </c>
-      <c r="J107" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K107" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B108" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C108" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D108" s="1">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="E108" s="1">
-        <v>302</v>
+        <v>513</v>
       </c>
       <c r="F108" s="1">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G108" s="1">
-        <v>0.1</v>
+        <v>8.6</v>
       </c>
       <c r="H108" s="1">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I108" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J108" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K108" s="1">
         <v>3</v>
@@ -4265,72 +4610,684 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B109" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="C109" s="1">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="D109" s="1">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="E109" s="1">
-        <v>914</v>
+        <v>229</v>
       </c>
       <c r="F109" s="1">
-        <v>50.4</v>
+        <v>30</v>
       </c>
       <c r="G109" s="1">
-        <v>12</v>
+        <v>0.1</v>
       </c>
       <c r="H109" s="1">
-        <v>57.6</v>
+        <v>11</v>
       </c>
       <c r="I109" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J109" s="1">
-        <v>50.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K109" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C110" s="1">
+        <v>6</v>
+      </c>
+      <c r="D110" s="1">
+        <v>100</v>
+      </c>
+      <c r="E110" s="1">
+        <v>262</v>
+      </c>
+      <c r="F110" s="1">
+        <v>21</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H110" s="1">
+        <v>12</v>
+      </c>
+      <c r="I110" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J110" s="1">
+        <v>16</v>
+      </c>
+      <c r="K110" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>138</v>
+      </c>
+      <c r="B111" t="s">
+        <v>140</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1</v>
+      </c>
+      <c r="D111" s="1">
+        <v>360</v>
+      </c>
+      <c r="E111" s="1">
+        <v>914</v>
+      </c>
+      <c r="F111" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="G111" s="1">
+        <v>12</v>
+      </c>
+      <c r="H111" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="I111" s="1">
+        <v>22</v>
+      </c>
+      <c r="J111" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="K111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>138</v>
+      </c>
+      <c r="B112" t="s">
+        <v>141</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1</v>
+      </c>
+      <c r="D112" s="1">
         <v>240</v>
       </c>
-      <c r="D110" s="1">
+      <c r="E112" s="1">
+        <v>754</v>
+      </c>
+      <c r="F112" s="1">
+        <v>41</v>
+      </c>
+      <c r="G112" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="H112" s="1">
+        <v>48</v>
+      </c>
+      <c r="I112" s="1">
+        <v>18</v>
+      </c>
+      <c r="J112" s="1">
+        <v>41</v>
+      </c>
+      <c r="K112" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B113" t="s">
+        <v>157</v>
+      </c>
+      <c r="C113" s="1">
+        <v>200</v>
+      </c>
+      <c r="D113" s="1">
+        <v>100</v>
+      </c>
+      <c r="E113" s="1">
+        <v>42</v>
+      </c>
+      <c r="F113" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="G113" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>171</v>
+      </c>
+      <c r="B114" t="s">
+        <v>158</v>
+      </c>
+      <c r="C114" s="1">
         <v>1</v>
       </c>
-      <c r="E110" s="1">
-        <v>754</v>
-      </c>
-      <c r="F110" s="1">
-        <v>41</v>
-      </c>
-      <c r="G110" s="1">
+      <c r="D114" s="1">
+        <v>60</v>
+      </c>
+      <c r="E114" s="1">
+        <v>255</v>
+      </c>
+      <c r="F114" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="G114" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="H114" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J114" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="K114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>159</v>
+      </c>
+      <c r="C115" s="1">
+        <v>100</v>
+      </c>
+      <c r="D115" s="1">
+        <v>100</v>
+      </c>
+      <c r="E115" s="1">
+        <v>136</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>3</v>
+      </c>
+      <c r="I115" s="1">
+        <v>1</v>
+      </c>
+      <c r="J115" s="1">
+        <v>27</v>
+      </c>
+      <c r="K115" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B116" t="s">
+        <v>160</v>
+      </c>
+      <c r="C116" s="1">
+        <v>170</v>
+      </c>
+      <c r="D116" s="1">
+        <v>100</v>
+      </c>
+      <c r="E116" s="1">
+        <v>85</v>
+      </c>
+      <c r="F116" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B117" t="s">
+        <v>161</v>
+      </c>
+      <c r="C117" s="1">
+        <v>100</v>
+      </c>
+      <c r="D117" s="1">
+        <v>100</v>
+      </c>
+      <c r="E117" s="1">
+        <v>29</v>
+      </c>
+      <c r="F117" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1">
+        <v>0</v>
+      </c>
+      <c r="K117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>162</v>
+      </c>
+      <c r="C118" s="1">
+        <v>100</v>
+      </c>
+      <c r="D118" s="1">
+        <v>100</v>
+      </c>
+      <c r="E118" s="1">
+        <v>21</v>
+      </c>
+      <c r="F118" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" t="s">
+        <v>163</v>
+      </c>
+      <c r="C119" s="1">
+        <v>220</v>
+      </c>
+      <c r="D119" s="1">
+        <v>100</v>
+      </c>
+      <c r="E119" s="1">
+        <v>252</v>
+      </c>
+      <c r="F119" s="1">
+        <v>30</v>
+      </c>
+      <c r="G119" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H119" s="1">
+        <v>11.6</v>
+      </c>
+      <c r="I119" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J119" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="K119" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" t="s">
+        <v>164</v>
+      </c>
+      <c r="C120" s="1">
+        <v>230</v>
+      </c>
+      <c r="D120" s="1">
+        <v>100</v>
+      </c>
+      <c r="E120" s="1">
+        <v>285</v>
+      </c>
+      <c r="F120" s="1">
+        <v>31</v>
+      </c>
+      <c r="G120" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H120" s="1">
+        <v>13</v>
+      </c>
+      <c r="I120" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J120" s="1">
+        <v>11</v>
+      </c>
+      <c r="K120" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>165</v>
+      </c>
+      <c r="C121" s="1">
+        <v>30</v>
+      </c>
+      <c r="D121" s="1">
+        <v>100</v>
+      </c>
+      <c r="E121" s="1">
+        <v>372</v>
+      </c>
+      <c r="F121" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G121" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="H121" s="1">
         <v>6.5</v>
       </c>
-      <c r="H110" s="1">
+      <c r="I121" s="1">
+        <v>4</v>
+      </c>
+      <c r="J121" s="1">
+        <v>70</v>
+      </c>
+      <c r="K121" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>153</v>
+      </c>
+      <c r="B122" t="s">
+        <v>166</v>
+      </c>
+      <c r="C122" s="1">
+        <v>160</v>
+      </c>
+      <c r="D122" s="1">
+        <v>100</v>
+      </c>
+      <c r="E122" s="1">
+        <v>128</v>
+      </c>
+      <c r="F122" s="1">
+        <v>0</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="I122" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J122" s="1">
+        <v>21</v>
+      </c>
+      <c r="K122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>153</v>
+      </c>
+      <c r="B123" t="s">
+        <v>167</v>
+      </c>
+      <c r="C123" s="1">
+        <v>190</v>
+      </c>
+      <c r="D123" s="1">
+        <v>100</v>
+      </c>
+      <c r="E123" s="1">
+        <v>91</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J123" s="1">
+        <v>19</v>
+      </c>
+      <c r="K123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>153</v>
+      </c>
+      <c r="B124" t="s">
+        <v>168</v>
+      </c>
+      <c r="C124" s="1">
+        <v>60</v>
+      </c>
+      <c r="D124" s="1">
+        <v>100</v>
+      </c>
+      <c r="E124" s="1">
+        <v>100</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I124" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J124" s="1">
+        <v>20</v>
+      </c>
+      <c r="K124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>170</v>
+      </c>
+      <c r="B125" t="s">
+        <v>169</v>
+      </c>
+      <c r="C125" s="1">
+        <v>20</v>
+      </c>
+      <c r="D125" s="1">
+        <v>100</v>
+      </c>
+      <c r="E125" s="1">
+        <v>226</v>
+      </c>
+      <c r="F125" s="1">
+        <v>4</v>
+      </c>
+      <c r="G125" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="H125" s="1">
+        <v>21</v>
+      </c>
+      <c r="I125" s="1">
+        <v>14</v>
+      </c>
+      <c r="J125" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K125" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>113</v>
+      </c>
+      <c r="B126" t="s">
+        <v>173</v>
+      </c>
+      <c r="C126" s="1">
+        <v>120</v>
+      </c>
+      <c r="D126" s="1">
+        <v>100</v>
+      </c>
+      <c r="E126" s="1">
+        <v>186</v>
+      </c>
+      <c r="F126" s="1">
+        <v>19</v>
+      </c>
+      <c r="G126" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H126" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I126" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J126" s="1">
+        <v>15</v>
+      </c>
+      <c r="K126" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>53</v>
+      </c>
+      <c r="B127" t="s">
+        <v>177</v>
+      </c>
+      <c r="C127" s="1">
+        <v>10</v>
+      </c>
+      <c r="D127" s="1">
+        <v>100</v>
+      </c>
+      <c r="E127" s="1">
+        <v>621</v>
+      </c>
+      <c r="F127" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4</v>
+      </c>
+      <c r="H127" s="1">
+        <v>53</v>
+      </c>
+      <c r="I127" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="J127" s="1">
+        <v>24</v>
+      </c>
+      <c r="K127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>53</v>
+      </c>
+      <c r="B128" t="s">
+        <v>176</v>
+      </c>
+      <c r="C128" s="1">
+        <v>15</v>
+      </c>
+      <c r="D128" s="1">
+        <v>100</v>
+      </c>
+      <c r="E128" s="1">
+        <v>579</v>
+      </c>
+      <c r="F128" s="1">
+        <v>12</v>
+      </c>
+      <c r="G128" s="1">
+        <v>2</v>
+      </c>
+      <c r="H128" s="1">
         <v>48</v>
       </c>
-      <c r="I110" s="1">
-        <v>18</v>
-      </c>
-      <c r="J110" s="1">
-        <v>41</v>
-      </c>
-      <c r="K110" s="1">
-        <v>4</v>
+      <c r="I128" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="J128" s="1">
+        <v>20</v>
+      </c>
+      <c r="K128" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="343" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05AC6B74-316C-3E45-8081-01EA56EFF671}"/>
+  <xr:revisionPtr revIDLastSave="355" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{963808EC-100D-D244-976C-613CEA458120}"/>
   <bookViews>
     <workbookView xWindow="630" yWindow="840" windowWidth="19575" windowHeight="7080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4581,10 +4581,10 @@
         <v>139</v>
       </c>
       <c r="C108" s="1">
+        <v>230</v>
+      </c>
+      <c r="D108" s="1">
         <v>1</v>
-      </c>
-      <c r="D108" s="1">
-        <v>230</v>
       </c>
       <c r="E108" s="1">
         <v>513</v>
@@ -4616,10 +4616,10 @@
         <v>175</v>
       </c>
       <c r="C109" s="1">
+        <v>70</v>
+      </c>
+      <c r="D109" s="1">
         <v>1</v>
-      </c>
-      <c r="D109" s="1">
-        <v>70</v>
       </c>
       <c r="E109" s="1">
         <v>229</v>
@@ -4651,10 +4651,10 @@
         <v>174</v>
       </c>
       <c r="C110" s="1">
+        <v>100</v>
+      </c>
+      <c r="D110" s="1">
         <v>6</v>
-      </c>
-      <c r="D110" s="1">
-        <v>100</v>
       </c>
       <c r="E110" s="1">
         <v>262</v>
@@ -4686,10 +4686,10 @@
         <v>140</v>
       </c>
       <c r="C111" s="1">
+        <v>360</v>
+      </c>
+      <c r="D111" s="1">
         <v>1</v>
-      </c>
-      <c r="D111" s="1">
-        <v>360</v>
       </c>
       <c r="E111" s="1">
         <v>914</v>
@@ -4721,10 +4721,10 @@
         <v>141</v>
       </c>
       <c r="C112" s="1">
+        <v>240</v>
+      </c>
+      <c r="D112" s="1">
         <v>1</v>
-      </c>
-      <c r="D112" s="1">
-        <v>240</v>
       </c>
       <c r="E112" s="1">
         <v>754</v>
@@ -4788,10 +4788,10 @@
         <v>158</v>
       </c>
       <c r="C114" s="1">
+        <v>60</v>
+      </c>
+      <c r="D114" s="1">
         <v>1</v>
-      </c>
-      <c r="D114" s="1">
-        <v>60</v>
       </c>
       <c r="E114" s="1">
         <v>255</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="355" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{963808EC-100D-D244-976C-613CEA458120}"/>
+  <xr:revisionPtr revIDLastSave="481" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA922948-9E6F-B14B-82DD-C93DDF7FE036}"/>
   <bookViews>
     <workbookView xWindow="630" yWindow="840" windowWidth="19575" windowHeight="7080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="187">
   <si>
     <t>kcal</t>
   </si>
@@ -390,9 +390,6 @@
     <t xml:space="preserve">panificio </t>
   </si>
   <si>
-    <t xml:space="preserve">bombolone krapfen </t>
-  </si>
-  <si>
     <t>panificio</t>
   </si>
   <si>
@@ -574,6 +571,24 @@
   </si>
   <si>
     <t>noci x9</t>
+  </si>
+  <si>
+    <t>Mcdonalds</t>
+  </si>
+  <si>
+    <t>wrap crispy</t>
+  </si>
+  <si>
+    <t>mcCrunchy</t>
+  </si>
+  <si>
+    <t>mc flurry caramello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yogurt caffè </t>
+  </si>
+  <si>
+    <t>bombolone krapfen cioccolato</t>
   </si>
 </sst>
 </file>
@@ -955,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.46875" customWidth="1"/>
@@ -970,7 +985,7 @@
         <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>110</v>
@@ -982,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -991,7 +1006,7 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
@@ -1075,7 +1090,7 @@
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="1">
         <v>40</v>
@@ -1585,7 +1600,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
@@ -1652,7 +1667,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
         <v>107</v>
@@ -1932,7 +1947,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C29" s="1">
         <v>55</v>
@@ -2340,7 +2355,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
         <v>30</v>
@@ -2410,7 +2425,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C44" s="1">
         <v>20</v>
@@ -2445,7 +2460,7 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C45" s="1">
         <v>30</v>
@@ -2477,10 +2492,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
         <v>148</v>
-      </c>
-      <c r="B46" t="s">
-        <v>149</v>
       </c>
       <c r="C46" s="1">
         <v>150</v>
@@ -2608,10 +2623,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" t="s">
         <v>145</v>
-      </c>
-      <c r="B50" t="s">
-        <v>146</v>
       </c>
       <c r="C50" s="1">
         <v>170</v>
@@ -2646,7 +2661,7 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="1">
         <v>200</v>
@@ -2678,7 +2693,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
         <v>105</v>
@@ -2713,7 +2728,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
         <v>106</v>
@@ -2783,7 +2798,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B55" t="s">
         <v>85</v>
@@ -2885,10 +2900,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
         <v>143</v>
-      </c>
-      <c r="B58" t="s">
-        <v>144</v>
       </c>
       <c r="C58" s="1">
         <v>60</v>
@@ -3185,7 +3200,7 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C67" s="1">
         <v>100</v>
@@ -3217,7 +3232,7 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C68" s="1">
         <v>12</v>
@@ -3281,7 +3296,7 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1">
         <v>240</v>
@@ -3313,7 +3328,7 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C71" s="1">
         <v>150</v>
@@ -3377,7 +3392,7 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C73" s="1">
         <v>21</v>
@@ -3668,136 +3683,136 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="C82" s="1">
         <v>125</v>
       </c>
       <c r="D82" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E82" s="1">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="F82" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G82" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H82" s="1">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="I82" s="1">
-        <v>3.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J82" s="1">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="K82" s="1">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C83" s="1">
         <v>125</v>
       </c>
       <c r="D83" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E83" s="1">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c r="F83" s="1">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="G83" s="1">
-        <v>1.3</v>
+        <v>13</v>
       </c>
       <c r="H83" s="1">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="I83" s="1">
-        <v>13.8</v>
+        <v>3.1</v>
       </c>
       <c r="J83" s="1">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="K83" s="1">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C84" s="1">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1">
-        <v>146</v>
+        <v>220</v>
       </c>
       <c r="F84" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="1">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="I84" s="1">
-        <v>2.2000000000000002</v>
+        <v>11</v>
       </c>
       <c r="J84" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K84" s="1">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C85" s="1">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1">
-        <v>553</v>
+        <v>146</v>
       </c>
       <c r="F85" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>42</v>
+        <v>6.2</v>
       </c>
       <c r="I85" s="1">
-        <v>3.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J85" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
@@ -3805,34 +3820,34 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="C86" s="1">
+        <v>30</v>
+      </c>
+      <c r="D86" s="1">
+        <v>100</v>
+      </c>
+      <c r="E86" s="1">
+        <v>553</v>
+      </c>
+      <c r="F86" s="1">
+        <v>28</v>
+      </c>
+      <c r="G86" s="1">
         <v>20</v>
       </c>
-      <c r="D86" s="1">
-        <v>100</v>
-      </c>
-      <c r="E86" s="1">
-        <v>364</v>
-      </c>
-      <c r="F86" s="1">
-        <v>60</v>
-      </c>
-      <c r="G86" s="1">
-        <v>1</v>
-      </c>
       <c r="H86" s="1">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="I86" s="1">
-        <v>1.1000000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="J86" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
@@ -3840,34 +3855,34 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="C87" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1">
-        <v>608</v>
+        <v>364</v>
       </c>
       <c r="F87" s="1">
+        <v>60</v>
+      </c>
+      <c r="G87" s="1">
+        <v>1</v>
+      </c>
+      <c r="H87" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="I87" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J87" s="1">
         <v>12</v>
-      </c>
-      <c r="G87" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="H87" s="1">
-        <v>47</v>
-      </c>
-      <c r="I87" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="J87" s="1">
-        <v>30</v>
       </c>
       <c r="K87" s="1">
         <v>0</v>
@@ -3875,142 +3890,142 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C88" s="1">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1">
-        <v>192</v>
+        <v>608</v>
       </c>
       <c r="F88" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G88" s="1">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="H88" s="1">
-        <v>8.6</v>
+        <v>47</v>
       </c>
       <c r="I88" s="1">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J88" s="1">
-        <v>12.8</v>
+        <v>30</v>
       </c>
       <c r="K88" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C89" s="1">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1">
-        <v>421</v>
+        <v>192</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H89" s="1">
-        <v>39</v>
+        <v>8.6</v>
       </c>
       <c r="I89" s="1">
-        <v>27</v>
+        <v>0.8</v>
       </c>
       <c r="J89" s="1">
-        <v>23</v>
+        <v>12.8</v>
       </c>
       <c r="K89" s="1">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1">
-        <v>54</v>
+        <v>421</v>
       </c>
       <c r="F90" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I90" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J90" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K90" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="C91" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1">
-        <v>683</v>
+        <v>54</v>
       </c>
       <c r="F91" s="1">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="G91" s="1">
-        <v>2.9</v>
+        <v>9.5</v>
       </c>
       <c r="H91" s="1">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I91" s="1">
-        <v>5.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="J91" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
@@ -4018,69 +4033,69 @@
         <v>53</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="C92" s="1">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1">
-        <v>54</v>
+        <v>683</v>
       </c>
       <c r="F92" s="1">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="G92" s="1">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="H92" s="1">
-        <v>0.3</v>
+        <v>66</v>
       </c>
       <c r="I92" s="1">
-        <v>0.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J92" s="1">
-        <v>9.1999999999999993</v>
+        <v>14</v>
       </c>
       <c r="K92" s="1">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C93" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="F93" s="1">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G93" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="H93" s="1">
         <v>0.3</v>
       </c>
-      <c r="H93" s="1">
-        <v>1</v>
-      </c>
       <c r="I93" s="1">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J93" s="1">
-        <v>19</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K93" s="1">
-        <v>2.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
@@ -4088,7 +4103,7 @@
         <v>87</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C94" s="1">
         <v>100</v>
@@ -4097,165 +4112,165 @@
         <v>100</v>
       </c>
       <c r="E94" s="1">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F94" s="1">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="G94" s="1">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H94" s="1">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I94" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J94" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K94" s="1">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C95" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="F95" s="1">
-        <v>0.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G95" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H95" s="1">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="I95" s="1">
-        <v>2.2000000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="J95" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K95" s="1">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C96" s="1">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F96" s="1">
-        <v>5.0999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="G96" s="1">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="H96" s="1">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I96" s="1">
-        <v>0.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J96" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K96" s="1">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C97" s="1">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1">
-        <v>451</v>
+        <v>67</v>
       </c>
       <c r="F97" s="1">
-        <v>0</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H97" s="1">
-        <v>44</v>
+        <v>4.7</v>
       </c>
       <c r="I97" s="1">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J97" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>9.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C98" s="1">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D98" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E98" s="1">
-        <v>295</v>
+        <v>451</v>
       </c>
       <c r="F98" s="1">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G98" s="1">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1">
+        <v>44</v>
+      </c>
+      <c r="I98" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="J98" s="1">
         <v>13</v>
       </c>
-      <c r="H98" s="1">
-        <v>16</v>
-      </c>
-      <c r="I98" s="1">
-        <v>8</v>
-      </c>
-      <c r="J98" s="1">
-        <v>5.5</v>
-      </c>
       <c r="K98" s="1">
-        <v>0.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
@@ -4263,42 +4278,42 @@
         <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C99" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D99" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E99" s="1">
-        <v>330</v>
+        <v>438</v>
       </c>
       <c r="F99" s="1">
-        <v>38</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="G99" s="1">
-        <v>15</v>
+        <v>20.6</v>
       </c>
       <c r="H99" s="1">
-        <v>17</v>
+        <v>28.1</v>
       </c>
       <c r="I99" s="1">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="J99" s="1">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="K99" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="C100" s="1">
         <v>75</v>
@@ -4307,33 +4322,33 @@
         <v>100</v>
       </c>
       <c r="E100" s="1">
-        <v>259</v>
+        <v>351</v>
       </c>
       <c r="F100" s="1">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G100" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H100" s="1">
-        <v>0.8</v>
+        <v>16</v>
       </c>
       <c r="I100" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J100" s="1">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="K100" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
-        <v>53</v>
+      <c r="A101" t="s">
+        <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C101" s="1">
         <v>75</v>
@@ -4342,232 +4357,232 @@
         <v>100</v>
       </c>
       <c r="E101" s="1">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="F101" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G101" s="1">
-        <v>4.5999999999999996</v>
+        <v>23</v>
       </c>
       <c r="H101" s="1">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="I101" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J101" s="1">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="K101" s="1">
         <v>1.4</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>126</v>
+      <c r="A102" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B102" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C102" s="1">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="F102" s="1">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G102" s="1">
-        <v>0.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="H102" s="1">
-        <v>8.3000000000000007</v>
+        <v>5.5</v>
       </c>
       <c r="I102" s="1">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J102" s="1">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="K102" s="1">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C103" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1">
-        <v>167</v>
+        <v>313</v>
       </c>
       <c r="F103" s="1">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="G103" s="1">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H103" s="1">
-        <v>10.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I103" s="1">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="J103" s="1">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="K103" s="1">
-        <v>0.35</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B104" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C104" s="1">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1">
-        <v>544</v>
+        <v>167</v>
       </c>
       <c r="F104" s="1">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>51</v>
+        <v>0.7</v>
       </c>
       <c r="H104" s="1">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="I104" s="1">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="J104" s="1">
-        <v>8.1</v>
+        <v>17</v>
       </c>
       <c r="K104" s="1">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B105" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C105" s="1">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1">
-        <v>225</v>
+        <v>544</v>
       </c>
       <c r="F105" s="1">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G105" s="1">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="H105" s="1">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I105" s="1">
-        <v>9.6999999999999993</v>
+        <v>5.7</v>
       </c>
       <c r="J105" s="1">
-        <v>3</v>
+        <v>8.1</v>
       </c>
       <c r="K105" s="1">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C106" s="1">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1">
-        <v>540</v>
+        <v>225</v>
       </c>
       <c r="F106" s="1">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="G106" s="1">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="H106" s="1">
-        <v>30.9</v>
+        <v>11</v>
       </c>
       <c r="I106" s="1">
-        <v>11</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J106" s="1">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="K106" s="1">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B107" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C107" s="1">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="F107" s="1">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H107" s="1">
-        <v>6.5</v>
+        <v>30.9</v>
       </c>
       <c r="I107" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J107" s="1">
-        <v>23</v>
+        <v>6.3</v>
       </c>
       <c r="K107" s="1">
         <v>0.1</v>
@@ -4575,69 +4590,69 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B108" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C108" s="1">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="D108" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E108" s="1">
-        <v>513</v>
+        <v>150</v>
       </c>
       <c r="F108" s="1">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>27</v>
+        <v>6.5</v>
       </c>
       <c r="I108" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J108" s="1">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K108" s="1">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>137</v>
+      </c>
+      <c r="B109" t="s">
         <v>138</v>
       </c>
-      <c r="B109" t="s">
-        <v>175</v>
-      </c>
       <c r="C109" s="1">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="D109" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E109" s="1">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="F109" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G109" s="1">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="H109" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I109" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J109" s="1">
-        <v>2.2999999999999998</v>
+        <v>12</v>
       </c>
       <c r="K109" s="1">
         <v>3</v>
@@ -4645,258 +4660,267 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B110" t="s">
         <v>174</v>
       </c>
       <c r="C110" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D110" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E110" s="1">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="F110" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G110" s="1">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H110" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I110" s="1">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J110" s="1">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K110" s="1">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="C111" s="1">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="D111" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E111" s="1">
-        <v>914</v>
+        <v>262</v>
       </c>
       <c r="F111" s="1">
-        <v>50.4</v>
+        <v>21</v>
       </c>
       <c r="G111" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H111" s="1">
         <v>12</v>
       </c>
-      <c r="H111" s="1">
-        <v>57.6</v>
-      </c>
       <c r="I111" s="1">
-        <v>22</v>
+        <v>1.5</v>
       </c>
       <c r="J111" s="1">
-        <v>50.4</v>
+        <v>16</v>
       </c>
       <c r="K111" s="1">
-        <v>4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B112" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C112" s="1">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="D112" s="1">
+        <v>100</v>
+      </c>
+      <c r="E112" s="1">
+        <v>236</v>
+      </c>
+      <c r="F112" s="1">
+        <v>15</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="H112" s="1">
+        <v>14</v>
+      </c>
+      <c r="I112" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="J112" s="1">
+        <v>12</v>
+      </c>
+      <c r="K112" s="1">
         <v>1</v>
       </c>
-      <c r="E112" s="1">
-        <v>754</v>
-      </c>
-      <c r="F112" s="1">
-        <v>41</v>
-      </c>
-      <c r="G112" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="H112" s="1">
-        <v>48</v>
-      </c>
-      <c r="I112" s="1">
-        <v>18</v>
-      </c>
-      <c r="J112" s="1">
-        <v>41</v>
-      </c>
-      <c r="K112" s="1">
-        <v>4</v>
-      </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>180</v>
+      </c>
       <c r="B113" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C113" s="1">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1">
-        <v>42</v>
+        <v>300</v>
       </c>
       <c r="F113" s="1">
-        <v>10.6</v>
+        <v>15</v>
       </c>
       <c r="G113" s="1">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="H113" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I113" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J113" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K113" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="B114" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C114" s="1">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="D114" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E114" s="1">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="F114" s="1">
-        <v>43.2</v>
+        <v>25</v>
       </c>
       <c r="G114" s="1">
-        <v>19.2</v>
+        <v>4</v>
       </c>
       <c r="H114" s="1">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I114" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="J114" s="1">
+        <v>10</v>
+      </c>
+      <c r="K114" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>137</v>
+      </c>
+      <c r="B115" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115" s="1">
+        <v>240</v>
+      </c>
+      <c r="D115" s="1">
+        <v>100</v>
+      </c>
+      <c r="E115" s="1">
+        <v>314</v>
+      </c>
+      <c r="F115" s="1">
+        <v>14</v>
+      </c>
+      <c r="G115" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="H115" s="1">
+        <v>20</v>
+      </c>
+      <c r="I115" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J115" s="1">
+        <v>17</v>
+      </c>
+      <c r="K115" s="1">
         <v>1.6</v>
       </c>
-      <c r="J114" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="K114" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B115" t="s">
-        <v>159</v>
-      </c>
-      <c r="C115" s="1">
-        <v>100</v>
-      </c>
-      <c r="D115" s="1">
-        <v>100</v>
-      </c>
-      <c r="E115" s="1">
-        <v>136</v>
-      </c>
-      <c r="F115" s="1">
-        <v>0</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0</v>
-      </c>
-      <c r="H115" s="1">
-        <v>3</v>
-      </c>
-      <c r="I115" s="1">
-        <v>1</v>
-      </c>
-      <c r="J115" s="1">
-        <v>27</v>
-      </c>
-      <c r="K115" s="1">
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>137</v>
+      </c>
+      <c r="B116" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="1">
+        <v>150</v>
+      </c>
+      <c r="D116" s="1">
+        <v>100</v>
+      </c>
+      <c r="E116" s="1">
+        <v>187</v>
+      </c>
+      <c r="F116" s="1">
+        <v>35</v>
+      </c>
+      <c r="G116" s="1">
+        <v>25</v>
+      </c>
+      <c r="H116" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B116" t="s">
-        <v>160</v>
-      </c>
-      <c r="C116" s="1">
-        <v>170</v>
-      </c>
-      <c r="D116" s="1">
-        <v>100</v>
-      </c>
-      <c r="E116" s="1">
-        <v>85</v>
-      </c>
-      <c r="F116" s="1">
+      <c r="I116" s="1">
         <v>2.6</v>
       </c>
-      <c r="G116" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="H116" s="1">
-        <v>0</v>
-      </c>
-      <c r="I116" s="1">
-        <v>0</v>
-      </c>
       <c r="J116" s="1">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K116" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C117" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F117" s="1">
-        <v>1.6</v>
+        <v>10.6</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -4912,169 +4936,163 @@
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>170</v>
+      </c>
       <c r="B118" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C118" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="F118" s="1">
-        <v>4.8</v>
+        <v>72</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I118" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J118" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K118" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>120</v>
-      </c>
       <c r="B119" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C119" s="1">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1">
-        <v>252</v>
+        <v>136</v>
       </c>
       <c r="F119" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G119" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H119" s="1">
-        <v>11.6</v>
+        <v>3</v>
       </c>
       <c r="I119" s="1">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J119" s="1">
-        <v>7.1</v>
+        <v>27</v>
       </c>
       <c r="K119" s="1">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>120</v>
-      </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C120" s="1">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="F120" s="1">
-        <v>31</v>
+        <v>2.6</v>
       </c>
       <c r="G120" s="1">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="H120" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I120" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J120" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C121" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1">
-        <v>372</v>
+        <v>29</v>
       </c>
       <c r="F121" s="1">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="G121" s="1">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H121" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I121" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J121" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>153</v>
-      </c>
       <c r="B122" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C122" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I122" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J122" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
         <v>0</v>
@@ -5082,174 +5100,171 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C123" s="1">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1">
-        <v>91</v>
+        <v>252</v>
       </c>
       <c r="F123" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G123" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H123" s="1">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="I123" s="1">
-        <v>0.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J123" s="1">
-        <v>19</v>
+        <v>7.1</v>
       </c>
       <c r="K123" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="B124" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C124" s="1">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
       </c>
       <c r="E124" s="1">
-        <v>100</v>
+        <v>285</v>
       </c>
       <c r="F124" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H124" s="1">
+        <v>13</v>
+      </c>
+      <c r="I124" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J124" s="1">
+        <v>11</v>
+      </c>
+      <c r="K124" s="1">
         <v>1.5</v>
       </c>
-      <c r="I124" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="J124" s="1">
-        <v>20</v>
-      </c>
-      <c r="K124" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>170</v>
-      </c>
       <c r="B125" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C125" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
       </c>
       <c r="E125" s="1">
-        <v>226</v>
+        <v>372</v>
       </c>
       <c r="F125" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="H125" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="I125" s="1">
         <v>4</v>
       </c>
-      <c r="G125" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="H125" s="1">
-        <v>21</v>
-      </c>
-      <c r="I125" s="1">
-        <v>14</v>
-      </c>
       <c r="J125" s="1">
-        <v>5.5</v>
+        <v>70</v>
       </c>
       <c r="K125" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="B126" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C126" s="1">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="F126" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G126" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I126" s="1">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J126" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="B127" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C127" s="1">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1">
-        <v>621</v>
+        <v>91</v>
       </c>
       <c r="F127" s="1">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="G127" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H127" s="1">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="I127" s="1">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J127" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K127" s="1">
         <v>0</v>
@@ -5257,36 +5272,176 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="B128" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C128" s="1">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1">
-        <v>579</v>
+        <v>100</v>
       </c>
       <c r="F128" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G128" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="1">
-        <v>48</v>
+        <v>1.5</v>
       </c>
       <c r="I128" s="1">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="J128" s="1">
         <v>20</v>
       </c>
       <c r="K128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>169</v>
+      </c>
+      <c r="B129" t="s">
+        <v>168</v>
+      </c>
+      <c r="C129" s="1">
+        <v>20</v>
+      </c>
+      <c r="D129" s="1">
+        <v>100</v>
+      </c>
+      <c r="E129" s="1">
+        <v>226</v>
+      </c>
+      <c r="F129" s="1">
+        <v>4</v>
+      </c>
+      <c r="G129" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="H129" s="1">
+        <v>21</v>
+      </c>
+      <c r="I129" s="1">
+        <v>14</v>
+      </c>
+      <c r="J129" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K129" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>113</v>
+      </c>
+      <c r="B130" t="s">
+        <v>172</v>
+      </c>
+      <c r="C130" s="1">
+        <v>120</v>
+      </c>
+      <c r="D130" s="1">
+        <v>100</v>
+      </c>
+      <c r="E130" s="1">
+        <v>186</v>
+      </c>
+      <c r="F130" s="1">
+        <v>19</v>
+      </c>
+      <c r="G130" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H130" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I130" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J130" s="1">
+        <v>15</v>
+      </c>
+      <c r="K130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>53</v>
+      </c>
+      <c r="B131" t="s">
+        <v>176</v>
+      </c>
+      <c r="C131" s="1">
+        <v>10</v>
+      </c>
+      <c r="D131" s="1">
+        <v>100</v>
+      </c>
+      <c r="E131" s="1">
+        <v>621</v>
+      </c>
+      <c r="F131" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G131" s="1">
+        <v>4</v>
+      </c>
+      <c r="H131" s="1">
+        <v>53</v>
+      </c>
+      <c r="I131" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="J131" s="1">
+        <v>24</v>
+      </c>
+      <c r="K131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>53</v>
+      </c>
+      <c r="B132" t="s">
+        <v>175</v>
+      </c>
+      <c r="C132" s="1">
+        <v>15</v>
+      </c>
+      <c r="D132" s="1">
+        <v>100</v>
+      </c>
+      <c r="E132" s="1">
+        <v>579</v>
+      </c>
+      <c r="F132" s="1">
+        <v>12</v>
+      </c>
+      <c r="G132" s="1">
+        <v>2</v>
+      </c>
+      <c r="H132" s="1">
+        <v>48</v>
+      </c>
+      <c r="I132" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="J132" s="1">
+        <v>20</v>
+      </c>
+      <c r="K132" s="1">
         <v>0</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="481" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA922948-9E6F-B14B-82DD-C93DDF7FE036}"/>
+  <xr:revisionPtr revIDLastSave="536" documentId="11_90CA257D9B83B663CFDA859302E9C06B7196E641" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B313F3-5F00-0941-BA7E-B23797048887}"/>
   <bookViews>
     <workbookView xWindow="630" yWindow="840" windowWidth="19575" windowHeight="7080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="192">
   <si>
     <t>kcal</t>
   </si>
@@ -589,6 +589,21 @@
   </si>
   <si>
     <t>bombolone krapfen cioccolato</t>
+  </si>
+  <si>
+    <t>macinato di tacchino</t>
+  </si>
+  <si>
+    <t>verdure cotte mix</t>
+  </si>
+  <si>
+    <t>peperoni arrostiti</t>
+  </si>
+  <si>
+    <t>pasta sfoglia (1/3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melanzana grigliata </t>
   </si>
 </sst>
 </file>
@@ -970,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.46875" customWidth="1"/>
@@ -5445,6 +5460,172 @@
         <v>0</v>
       </c>
     </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>87</v>
+      </c>
+      <c r="B133" t="s">
+        <v>186</v>
+      </c>
+      <c r="C133" s="1">
+        <v>135</v>
+      </c>
+      <c r="D133" s="1">
+        <v>100</v>
+      </c>
+      <c r="E133" s="1">
+        <v>137</v>
+      </c>
+      <c r="F133" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="I133" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="J133" s="1">
+        <v>17</v>
+      </c>
+      <c r="K133" s="1">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>71</v>
+      </c>
+      <c r="B134" t="s">
+        <v>189</v>
+      </c>
+      <c r="C134" s="1">
+        <v>70</v>
+      </c>
+      <c r="D134" s="1">
+        <v>100</v>
+      </c>
+      <c r="E134" s="1">
+        <v>388</v>
+      </c>
+      <c r="F134" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="G134" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H134" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="I134" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="J134" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K134" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>187</v>
+      </c>
+      <c r="C135" s="1">
+        <v>200</v>
+      </c>
+      <c r="D135" s="1">
+        <v>100</v>
+      </c>
+      <c r="E135" s="1">
+        <v>50</v>
+      </c>
+      <c r="F135" s="1">
+        <v>8</v>
+      </c>
+      <c r="G135" s="1">
+        <v>4</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I135" s="1">
+        <v>0</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B136" t="s">
+        <v>188</v>
+      </c>
+      <c r="C136" s="1">
+        <v>180</v>
+      </c>
+      <c r="D136" s="1">
+        <v>100</v>
+      </c>
+      <c r="E136" s="1">
+        <v>45</v>
+      </c>
+      <c r="F136" s="1">
+        <v>7</v>
+      </c>
+      <c r="G136" s="1">
+        <v>6</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I136" s="1">
+        <v>0</v>
+      </c>
+      <c r="J136" s="1">
+        <v>1</v>
+      </c>
+      <c r="K136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>190</v>
+      </c>
+      <c r="C137" s="1">
+        <v>200</v>
+      </c>
+      <c r="D137" s="1">
+        <v>100</v>
+      </c>
+      <c r="E137" s="1">
+        <v>35</v>
+      </c>
+      <c r="F137" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G137" s="1">
+        <v>3</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="I137" s="1">
+        <v>0</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K137" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
